--- a/AAII_Financials/Yearly/MTB_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/MTB_YR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Yearly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Yearly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,12 +17,12 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="153" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="157" uniqueCount="92">
   <si>
     <t>MTB</t>
   </si>
@@ -656,113 +656,119 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:P102"/>
+  <dimension ref="A5:Q102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="11" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="12" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E7" s="2">
         <v>44926</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>44561</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44196</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>43830</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>43465</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>43100</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>42735</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>42369</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>42004</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>41639</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>41274</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>40908</v>
       </c>
-      <c r="P7" s="2"/>
-    </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q7" s="2"/>
+    </row>
+    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>10224000</v>
+      </c>
+      <c r="E8" s="3">
         <v>6247100</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>3938800</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>4192700</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>4879600</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>4598700</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>4167800</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>3895900</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>3170800</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>2956900</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>2957300</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>2941700</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>2792100</v>
       </c>
-      <c r="P8" s="3"/>
-    </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q8" s="3"/>
+    </row>
+    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
@@ -802,9 +808,12 @@
       <c r="O9" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="P9" s="3"/>
-    </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q9" s="3"/>
+    </row>
+    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -844,9 +853,12 @@
       <c r="O10" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="P10" s="3"/>
-    </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q10" s="3"/>
+    </row>
+    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -863,8 +875,9 @@
       <c r="N11" s="3"/>
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
-    </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q11" s="3"/>
+    </row>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -904,9 +917,12 @@
       <c r="O12" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="P12" s="3"/>
-    </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P12" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q12" s="3"/>
+    </row>
+    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -946,9 +962,12 @@
       <c r="O13" s="3">
         <v>0</v>
       </c>
-      <c r="P13" s="3"/>
-    </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P13" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q13" s="3"/>
+    </row>
+    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -988,51 +1007,57 @@
       <c r="O14" s="3">
         <v>0</v>
       </c>
-      <c r="P14" s="3"/>
-    </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P14" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q14" s="3"/>
+    </row>
+    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>-62000</v>
+      </c>
+      <c r="E15" s="3">
         <v>-55600</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>-10200</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>-14900</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>-19500</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>-24500</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>-31400</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>-42600</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>-26400</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>-33800</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>-46900</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>-60600</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>-61600</v>
       </c>
-      <c r="P15" s="3"/>
-    </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q15" s="3"/>
+    </row>
+    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1046,92 +1071,99 @@
       <c r="N16" s="3"/>
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
-    </row>
-    <row r="17" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q16" s="3"/>
+    </row>
+    <row r="17" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>3754000</v>
+      </c>
+      <c r="E17" s="3">
         <v>942200</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>114000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>326400</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>925300</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>658400</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>554800</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>616000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>498300</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>404400</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>469100</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>547200</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>672300</v>
       </c>
-      <c r="P17" s="3"/>
-    </row>
-    <row r="18" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q17" s="3"/>
+    </row>
+    <row r="18" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>6470000</v>
+      </c>
+      <c r="E18" s="3">
         <v>5305000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>3824800</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>3866300</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>3954300</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>3940300</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>3613000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>3279900</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>2672600</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>2552400</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>2488200</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>2394500</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>2119800</v>
       </c>
-      <c r="P18" s="3"/>
-    </row>
-    <row r="19" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q18" s="3"/>
+    </row>
+    <row r="19" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1148,92 +1180,99 @@
       <c r="N19" s="3"/>
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
-    </row>
-    <row r="20" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q19" s="3"/>
+    </row>
+    <row r="20" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-2851000</v>
+      </c>
+      <c r="E20" s="3">
         <v>-2693800</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-1369600</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-2096800</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-1407000</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-1432100</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-1289200</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-1221500</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-997900</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-910200</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-770700</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-842000</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-895200</v>
       </c>
-      <c r="P20" s="3"/>
-    </row>
-    <row r="21" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q20" s="3"/>
+    </row>
+    <row r="21" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>3985000</v>
+      </c>
+      <c r="E21" s="3">
         <v>2948800</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>2689600</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>2005000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>2776700</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>2637600</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>2464800</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>2208000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>1800100</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>1772600</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>1855900</v>
       </c>
-      <c r="N21" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="O21" s="3">
+      <c r="O21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P21" s="3">
         <v>1366500</v>
       </c>
-      <c r="P21" s="3"/>
-    </row>
-    <row r="22" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q21" s="3"/>
+    </row>
+    <row r="22" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1273,93 +1312,102 @@
       <c r="O22" s="3">
         <v>0</v>
       </c>
-      <c r="P22" s="3"/>
-    </row>
-    <row r="23" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P22" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q22" s="3"/>
+    </row>
+    <row r="23" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>3619000</v>
+      </c>
+      <c r="E23" s="3">
         <v>2611100</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>2455100</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>1769500</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>2547300</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>2508200</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>2323900</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>2058400</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>1674700</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>1642200</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>1717500</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>1552500</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>1224600</v>
       </c>
-      <c r="P23" s="3"/>
-    </row>
-    <row r="24" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q23" s="3"/>
+    </row>
+    <row r="24" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>878000</v>
+      </c>
+      <c r="E24" s="3">
         <v>619500</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>596400</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>416400</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>618100</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>590200</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>830100</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>743300</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>595000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>576000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>579100</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>523000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>365100</v>
       </c>
-      <c r="P24" s="3"/>
-    </row>
-    <row r="25" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q24" s="3"/>
+    </row>
+    <row r="25" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1399,93 +1447,102 @@
       <c r="O25" s="3">
         <v>0</v>
       </c>
-      <c r="P25" s="3"/>
-    </row>
-    <row r="26" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P25" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q25" s="3"/>
+    </row>
+    <row r="26" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>2741000</v>
+      </c>
+      <c r="E26" s="3">
         <v>1991700</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>1858700</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>1353200</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>1929100</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>1918100</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>1493700</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>1315100</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>1079700</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>1066200</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>1138500</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>1029500</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>859500</v>
       </c>
-      <c r="P26" s="3"/>
-    </row>
-    <row r="27" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q26" s="3"/>
+    </row>
+    <row r="27" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>2636000</v>
+      </c>
+      <c r="E27" s="3">
         <v>1891500</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>1777000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>1279100</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>1849500</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>1836000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>1412900</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>1223500</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>987700</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>978500</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>1062400</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>953400</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>781700</v>
       </c>
-      <c r="P27" s="3"/>
-    </row>
-    <row r="28" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q27" s="3"/>
+    </row>
+    <row r="28" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1525,9 +1582,12 @@
       <c r="O28" s="3">
         <v>0</v>
       </c>
-      <c r="P28" s="3"/>
-    </row>
-    <row r="29" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P28" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q28" s="3"/>
+    </row>
+    <row r="29" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1546,12 +1606,12 @@
       <c r="H29" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="I29" s="3">
+      <c r="I29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J29" s="3">
         <v>-85400</v>
       </c>
-      <c r="J29" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="K29" s="3" t="s">
         <v>5</v>
       </c>
@@ -1567,9 +1627,12 @@
       <c r="O29" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="P29" s="3"/>
-    </row>
-    <row r="30" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q29" s="3"/>
+    </row>
+    <row r="30" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1609,9 +1672,12 @@
       <c r="O30" s="3">
         <v>0</v>
       </c>
-      <c r="P30" s="3"/>
-    </row>
-    <row r="31" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P30" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q30" s="3"/>
+    </row>
+    <row r="31" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1651,93 +1717,102 @@
       <c r="O31" s="3">
         <v>0</v>
       </c>
-      <c r="P31" s="3"/>
-    </row>
-    <row r="32" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P31" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q31" s="3"/>
+    </row>
+    <row r="32" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>2851000</v>
+      </c>
+      <c r="E32" s="3">
         <v>2693800</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>1369600</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>2096800</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>1407000</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>1432100</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>1289200</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>1221500</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>997900</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>910200</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>770700</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>842000</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>895200</v>
       </c>
-      <c r="P32" s="3"/>
-    </row>
-    <row r="33" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q32" s="3"/>
+    </row>
+    <row r="33" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>2636000</v>
+      </c>
+      <c r="E33" s="3">
         <v>1891500</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>1777000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>1279100</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>1849500</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>1836000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>1327500</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>1223500</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>987700</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>978500</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>1062400</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>953400</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>781700</v>
       </c>
-      <c r="P33" s="3"/>
-    </row>
-    <row r="34" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q33" s="3"/>
+    </row>
+    <row r="34" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1777,98 +1852,107 @@
       <c r="O34" s="3">
         <v>0</v>
       </c>
-      <c r="P34" s="3"/>
-    </row>
-    <row r="35" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P34" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q34" s="3"/>
+    </row>
+    <row r="35" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>2636000</v>
+      </c>
+      <c r="E35" s="3">
         <v>1891500</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>1777000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>1279100</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>1849500</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>1836000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>1327500</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>1223500</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>987700</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>978500</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>1062400</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>953400</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>781700</v>
       </c>
-      <c r="P35" s="3"/>
-    </row>
-    <row r="37" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q35" s="3"/>
+    </row>
+    <row r="37" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E38" s="2">
         <v>44926</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>44561</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44196</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>43830</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>43465</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>43100</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>42735</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>42369</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>42004</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>41639</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>41274</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>40908</v>
       </c>
-      <c r="P38" s="2"/>
-    </row>
-    <row r="39" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q38" s="2"/>
+    </row>
+    <row r="39" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1885,8 +1969,9 @@
       <c r="N39" s="3"/>
       <c r="O39" s="3"/>
       <c r="P39" s="3"/>
-    </row>
-    <row r="40" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q39" s="3"/>
+    </row>
+    <row r="40" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1903,92 +1988,99 @@
       <c r="N40" s="3"/>
       <c r="O40" s="3"/>
       <c r="P40" s="3"/>
-    </row>
-    <row r="41" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q40" s="3"/>
+    </row>
+    <row r="41" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>1731000</v>
+      </c>
+      <c r="E41" s="3">
         <v>1517200</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>1337600</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>1552700</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>1432800</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>1605400</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>1420900</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>1320500</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>1368000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>1290000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>1573400</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>1983600</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>1449500</v>
       </c>
-      <c r="P41" s="3"/>
-    </row>
-    <row r="42" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q41" s="3"/>
+    </row>
+    <row r="42" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>29302000</v>
+      </c>
+      <c r="E42" s="3">
         <v>26011500</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>42805700</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>25206500</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>8588100</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>9113500</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>5704900</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>6064700</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>8672000</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>7481500</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>2816200</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>924600</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>1086500</v>
       </c>
-      <c r="P42" s="3"/>
-    </row>
-    <row r="43" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q42" s="3"/>
+    </row>
+    <row r="43" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -2028,9 +2120,12 @@
       <c r="O43" s="3">
         <v>0</v>
       </c>
-      <c r="P43" s="3"/>
-    </row>
-    <row r="44" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P43" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q43" s="3"/>
+    </row>
+    <row r="44" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2070,9 +2165,12 @@
       <c r="O44" s="3">
         <v>0</v>
       </c>
-      <c r="P44" s="3"/>
-    </row>
-    <row r="45" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P44" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q44" s="3"/>
+    </row>
+    <row r="45" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -2112,9 +2210,12 @@
       <c r="O45" s="3">
         <v>0</v>
       </c>
-      <c r="P45" s="3"/>
-    </row>
-    <row r="46" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P45" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q45" s="3"/>
+    </row>
+    <row r="46" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
@@ -2154,9 +2255,12 @@
       <c r="O46" s="3">
         <v>0</v>
       </c>
-      <c r="P46" s="3"/>
-    </row>
-    <row r="47" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P46" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q46" s="3"/>
+    </row>
+    <row r="47" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -2196,93 +2300,102 @@
       <c r="O47" s="3">
         <v>0</v>
       </c>
-      <c r="P47" s="3"/>
-    </row>
-    <row r="48" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P47" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q47" s="3"/>
+    </row>
+    <row r="48" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>1739000</v>
+      </c>
+      <c r="E48" s="3">
         <v>1653600</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>1144800</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>1161600</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>1140900</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>647400</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>646500</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>675300</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>666700</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>613000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>633500</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>594700</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>581400</v>
       </c>
-      <c r="P48" s="3"/>
-    </row>
-    <row r="49" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q48" s="3"/>
+    </row>
+    <row r="49" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>8612000</v>
+      </c>
+      <c r="E49" s="3">
         <v>8699500</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>4597100</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>4607300</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>4622100</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>4640200</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>4664700</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>4690800</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>4733400</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>3559700</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>3593500</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>3640400</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>3701000</v>
       </c>
-      <c r="P49" s="3"/>
-    </row>
-    <row r="50" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q49" s="3"/>
+    </row>
+    <row r="50" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2322,9 +2435,12 @@
       <c r="O50" s="3">
         <v>0</v>
       </c>
-      <c r="P50" s="3"/>
-    </row>
-    <row r="51" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P50" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q50" s="3"/>
+    </row>
+    <row r="51" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2364,9 +2480,12 @@
       <c r="O51" s="3">
         <v>0</v>
       </c>
-      <c r="P51" s="3"/>
-    </row>
-    <row r="52" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P51" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q51" s="3"/>
+    </row>
+    <row r="52" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -2406,9 +2525,12 @@
       <c r="O52" s="3">
         <v>0</v>
       </c>
-      <c r="P52" s="3"/>
-    </row>
-    <row r="53" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P52" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q52" s="3"/>
+    </row>
+    <row r="53" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2448,51 +2570,57 @@
       <c r="O53" s="3">
         <v>0</v>
       </c>
-      <c r="P53" s="3"/>
-    </row>
-    <row r="54" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P53" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q53" s="3"/>
+    </row>
+    <row r="54" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>208264000</v>
+      </c>
+      <c r="E54" s="3">
         <v>200730000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>155107000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>142601000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>119873000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>120097000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>118594000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>123449000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>122788000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>96685500</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>85162400</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>83008800</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>77924300</v>
       </c>
-      <c r="P54" s="3"/>
-    </row>
-    <row r="55" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q54" s="3"/>
+    </row>
+    <row r="55" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2509,8 +2637,9 @@
       <c r="N55" s="3"/>
       <c r="O55" s="3"/>
       <c r="P55" s="3"/>
-    </row>
-    <row r="56" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q55" s="3"/>
+    </row>
+    <row r="56" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2527,50 +2656,54 @@
       <c r="N56" s="3"/>
       <c r="O56" s="3"/>
       <c r="P56" s="3"/>
-    </row>
-    <row r="57" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q56" s="3"/>
+    </row>
+    <row r="57" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>3799000</v>
+      </c>
+      <c r="E57" s="3">
         <v>3668500</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>1696900</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>1699400</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>1762800</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>1446700</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>1454800</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>1634600</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>1708100</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>1355900</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>1114700</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>1512700</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>1790100</v>
       </c>
-      <c r="P57" s="3"/>
-    </row>
-    <row r="58" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q57" s="3"/>
+    </row>
+    <row r="58" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -2610,27 +2743,30 @@
       <c r="O58" s="3">
         <v>0</v>
       </c>
-      <c r="P58" s="3"/>
-    </row>
-    <row r="59" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P58" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q58" s="3"/>
+    </row>
+    <row r="59" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>717000</v>
+      </c>
+      <c r="E59" s="3">
         <v>709000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>431000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>467000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>487600</v>
       </c>
-      <c r="H59" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="I59" s="3" t="s">
         <v>5</v>
       </c>
@@ -2646,15 +2782,18 @@
       <c r="M59" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="N59" s="3">
-        <v>0</v>
+      <c r="N59" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="O59" s="3">
         <v>0</v>
       </c>
-      <c r="P59" s="3"/>
-    </row>
-    <row r="60" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P59" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q59" s="3"/>
+    </row>
+    <row r="60" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
@@ -2694,51 +2833,57 @@
       <c r="O60" s="3">
         <v>0</v>
       </c>
-      <c r="P60" s="3"/>
-    </row>
-    <row r="61" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P60" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q60" s="3"/>
+    </row>
+    <row r="61" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>8201000</v>
+      </c>
+      <c r="E61" s="3">
         <v>3964500</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>3485400</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>4382200</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>6986200</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>8444900</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>8141400</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>9493800</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>10653900</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>9007000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>5108900</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>3177700</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>3887800</v>
       </c>
-      <c r="P61" s="3"/>
-    </row>
-    <row r="62" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q61" s="3"/>
+    </row>
+    <row r="62" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -2778,9 +2923,12 @@
       <c r="O62" s="3">
         <v>0</v>
       </c>
-      <c r="P62" s="3"/>
-    </row>
-    <row r="63" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P62" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q62" s="3"/>
+    </row>
+    <row r="63" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2820,9 +2968,12 @@
       <c r="O63" s="3">
         <v>0</v>
       </c>
-      <c r="P63" s="3"/>
-    </row>
-    <row r="64" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P63" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q63" s="3"/>
+    </row>
+    <row r="64" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2862,9 +3013,12 @@
       <c r="O64" s="3">
         <v>0</v>
       </c>
-      <c r="P64" s="3"/>
-    </row>
-    <row r="65" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P64" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q64" s="3"/>
+    </row>
+    <row r="65" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2904,51 +3058,57 @@
       <c r="O65" s="3">
         <v>0</v>
       </c>
-      <c r="P65" s="3"/>
-    </row>
-    <row r="66" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P65" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q65" s="3"/>
+    </row>
+    <row r="66" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>181307000</v>
+      </c>
+      <c r="E66" s="3">
         <v>175412000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>137204000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>126414000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>104156000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>104637000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>102343000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>106963000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>106615000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>84349600</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>73856900</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>72806200</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>68653100</v>
       </c>
-      <c r="P66" s="3"/>
-    </row>
-    <row r="67" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q66" s="3"/>
+    </row>
+    <row r="67" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2965,8 +3125,9 @@
       <c r="N67" s="3"/>
       <c r="O67" s="3"/>
       <c r="P67" s="3"/>
-    </row>
-    <row r="68" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q67" s="3"/>
+    </row>
+    <row r="68" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3006,9 +3167,12 @@
       <c r="O68" s="3">
         <v>0</v>
       </c>
-      <c r="P68" s="3"/>
-    </row>
-    <row r="69" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P68" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q68" s="3"/>
+    </row>
+    <row r="69" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3048,26 +3212,29 @@
       <c r="O69" s="3">
         <v>0</v>
       </c>
-      <c r="P69" s="3"/>
-    </row>
-    <row r="70" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P69" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q69" s="3"/>
+    </row>
+    <row r="70" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
       <c r="D70" s="3">
+        <v>2011000</v>
+      </c>
+      <c r="E70" s="3">
         <v>2010600</v>
       </c>
-      <c r="E70" s="3">
+      <c r="F70" s="3">
         <v>1750000</v>
-      </c>
-      <c r="F70" s="3">
-        <v>1250000</v>
       </c>
       <c r="G70" s="3">
         <v>1250000</v>
       </c>
       <c r="H70" s="3">
-        <v>1231500</v>
+        <v>1250000</v>
       </c>
       <c r="I70" s="3">
         <v>1231500</v>
@@ -3082,17 +3249,20 @@
         <v>1231500</v>
       </c>
       <c r="M70" s="3">
+        <v>1231500</v>
+      </c>
+      <c r="N70" s="3">
         <v>881500</v>
       </c>
-      <c r="N70" s="3">
+      <c r="O70" s="3">
         <v>872500</v>
       </c>
-      <c r="O70" s="3">
+      <c r="P70" s="3">
         <v>864600</v>
       </c>
-      <c r="P70" s="3"/>
-    </row>
-    <row r="71" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q70" s="3"/>
+    </row>
+    <row r="71" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3132,51 +3302,57 @@
       <c r="O71" s="3">
         <v>0</v>
       </c>
-      <c r="P71" s="3"/>
-    </row>
-    <row r="72" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P71" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q71" s="3"/>
+    </row>
+    <row r="72" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>17524000</v>
+      </c>
+      <c r="E72" s="3">
         <v>15754000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>14646400</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>13444400</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>12820900</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>11516700</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>10164800</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>9222500</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>8430500</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>7807100</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>7188000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>6477300</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>5867200</v>
       </c>
-      <c r="P72" s="3"/>
-    </row>
-    <row r="73" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q72" s="3"/>
+    </row>
+    <row r="73" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3216,9 +3392,12 @@
       <c r="O73" s="3">
         <v>0</v>
       </c>
-      <c r="P73" s="3"/>
-    </row>
-    <row r="74" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P73" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q73" s="3"/>
+    </row>
+    <row r="74" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3258,9 +3437,12 @@
       <c r="O74" s="3">
         <v>0</v>
       </c>
-      <c r="P74" s="3"/>
-    </row>
-    <row r="75" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P74" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q74" s="3"/>
+    </row>
+    <row r="75" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3300,51 +3482,57 @@
       <c r="O75" s="3">
         <v>0</v>
       </c>
-      <c r="P75" s="3"/>
-    </row>
-    <row r="76" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P75" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q75" s="3"/>
+    </row>
+    <row r="76" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>24946000</v>
+      </c>
+      <c r="E76" s="3">
         <v>23307400</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>16153400</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>14937300</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>14466600</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>14228700</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>15019300</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>15255100</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>14941800</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>11104400</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>10424000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>9330100</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>8406600</v>
       </c>
-      <c r="P76" s="3"/>
-    </row>
-    <row r="77" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q76" s="3"/>
+    </row>
+    <row r="77" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3384,98 +3572,107 @@
       <c r="O77" s="3">
         <v>0</v>
       </c>
-      <c r="P77" s="3"/>
-    </row>
-    <row r="79" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P77" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q77" s="3"/>
+    </row>
+    <row r="79" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E80" s="2">
         <v>44926</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>44561</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44196</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>43830</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>43465</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>43100</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>42735</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>42369</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>42004</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>41639</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>41274</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>40908</v>
       </c>
-      <c r="P80" s="2"/>
-    </row>
-    <row r="81" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q80" s="2"/>
+    </row>
+    <row r="81" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>2636000</v>
+      </c>
+      <c r="E81" s="3">
         <v>1891500</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>1777000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>1279100</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>1849500</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>1836000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>1327500</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>1223500</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>987700</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>978500</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>1062400</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>953400</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>781700</v>
       </c>
-      <c r="P81" s="3"/>
-    </row>
-    <row r="82" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q81" s="3"/>
+    </row>
+    <row r="82" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3492,50 +3689,54 @@
       <c r="N82" s="3"/>
       <c r="O82" s="3"/>
       <c r="P82" s="3"/>
-    </row>
-    <row r="83" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q82" s="3"/>
+    </row>
+    <row r="83" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>366000</v>
+      </c>
+      <c r="E83" s="3">
         <v>337700</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>234400</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>235500</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>229400</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>129400</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>141000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>149600</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>125400</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>130300</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>138400</v>
       </c>
-      <c r="N83" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="O83" s="3">
+      <c r="O83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P83" s="3">
         <v>141900</v>
       </c>
-      <c r="P83" s="3"/>
-    </row>
-    <row r="84" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q83" s="3"/>
+    </row>
+    <row r="84" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3575,9 +3776,12 @@
       <c r="O84" s="3">
         <v>0</v>
       </c>
-      <c r="P84" s="3"/>
-    </row>
-    <row r="85" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P84" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q84" s="3"/>
+    </row>
+    <row r="85" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3617,9 +3821,12 @@
       <c r="O85" s="3">
         <v>0</v>
       </c>
-      <c r="P85" s="3"/>
-    </row>
-    <row r="86" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P85" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q85" s="3"/>
+    </row>
+    <row r="86" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3659,9 +3866,12 @@
       <c r="O86" s="3">
         <v>0</v>
       </c>
-      <c r="P86" s="3"/>
-    </row>
-    <row r="87" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P86" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q86" s="3"/>
+    </row>
+    <row r="87" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3701,9 +3911,12 @@
       <c r="O87" s="3">
         <v>0</v>
       </c>
-      <c r="P87" s="3"/>
-    </row>
-    <row r="88" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P87" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q87" s="3"/>
+    </row>
+    <row r="88" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3743,51 +3956,57 @@
       <c r="O88" s="3">
         <v>0</v>
       </c>
-      <c r="P88" s="3"/>
-    </row>
-    <row r="89" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P88" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q88" s="3"/>
+    </row>
+    <row r="89" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>3905000</v>
+      </c>
+      <c r="E89" s="3">
         <v>4573700</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>2715000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>789200</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>2357600</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>2089900</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>2781900</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>1183400</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>1742400</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>1099000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>932300</v>
-      </c>
-      <c r="N89" s="3">
-        <v>1772200</v>
       </c>
       <c r="O89" s="3">
         <v>1772200</v>
       </c>
-      <c r="P89" s="3"/>
-    </row>
-    <row r="90" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P89" s="3">
+        <v>1772200</v>
+      </c>
+      <c r="Q89" s="3"/>
+    </row>
+    <row r="90" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3804,50 +4023,54 @@
       <c r="N90" s="3"/>
       <c r="O90" s="3"/>
       <c r="P90" s="3"/>
-    </row>
-    <row r="91" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q90" s="3"/>
+    </row>
+    <row r="91" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-256000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-214400</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-149200</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-172300</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-178000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-97700</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-79000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-107700</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-81900</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-73200</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-129600</v>
-      </c>
-      <c r="N91" s="3">
-        <v>-70000</v>
       </c>
       <c r="O91" s="3">
         <v>-70000</v>
       </c>
-      <c r="P91" s="3"/>
-    </row>
-    <row r="92" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P91" s="3">
+        <v>-70000</v>
+      </c>
+      <c r="Q91" s="3"/>
+    </row>
+    <row r="92" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3887,9 +4110,12 @@
       <c r="O92" s="3">
         <v>0</v>
       </c>
-      <c r="P92" s="3"/>
-    </row>
-    <row r="93" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P92" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q92" s="3"/>
+    </row>
+    <row r="93" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3929,51 +4155,57 @@
       <c r="O93" s="3">
         <v>0</v>
       </c>
-      <c r="P93" s="3"/>
-    </row>
-    <row r="94" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P93" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q93" s="3"/>
+    </row>
+    <row r="94" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-7874000</v>
+      </c>
+      <c r="E94" s="3">
         <v>16592700</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-13631600</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-22020500</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>727000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-1410100</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>3394900</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-720800</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>7714300</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-11710400</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-2203600</v>
       </c>
-      <c r="N94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="O94" s="3">
+      <c r="O94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P94" s="3">
         <v>368900</v>
       </c>
-      <c r="P94" s="3"/>
-    </row>
-    <row r="95" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q94" s="3"/>
+    </row>
+    <row r="95" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3990,50 +4222,54 @@
       <c r="N95" s="3"/>
       <c r="O95" s="3"/>
       <c r="P95" s="3"/>
-    </row>
-    <row r="96" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q95" s="3"/>
+    </row>
+    <row r="96" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>-968000</v>
+      </c>
+      <c r="E96" s="3">
         <v>-881000</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>-648500</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>-636400</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>-619600</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>-582900</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>-530100</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>-523200</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>-456300</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>-441400</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>-418800</v>
-      </c>
-      <c r="N96" s="3">
-        <v>-398300</v>
       </c>
       <c r="O96" s="3">
         <v>-398300</v>
       </c>
-      <c r="P96" s="3"/>
-    </row>
-    <row r="97" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P96" s="3">
+        <v>-398300</v>
+      </c>
+      <c r="Q96" s="3"/>
+    </row>
+    <row r="97" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4073,9 +4309,12 @@
       <c r="O97" s="3">
         <v>0</v>
       </c>
-      <c r="P97" s="3"/>
-    </row>
-    <row r="98" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P97" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q97" s="3"/>
+    </row>
+    <row r="98" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4115,9 +4354,12 @@
       <c r="O98" s="3">
         <v>0</v>
       </c>
-      <c r="P98" s="3"/>
-    </row>
-    <row r="99" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P98" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q98" s="3"/>
+    </row>
+    <row r="99" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4157,51 +4399,57 @@
       <c r="O99" s="3">
         <v>0</v>
       </c>
-      <c r="P99" s="3"/>
-    </row>
-    <row r="100" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P99" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q99" s="3"/>
+    </row>
+    <row r="100" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>4180000</v>
+      </c>
+      <c r="E100" s="3">
         <v>-20983800</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>10701500</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>21347700</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-3253700</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-495300</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-6076500</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-510100</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-9462000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>10311800</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>957600</v>
       </c>
-      <c r="N100" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="O100" s="3">
+      <c r="O100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P100" s="3">
         <v>-1622500</v>
       </c>
-      <c r="P100" s="3"/>
-    </row>
-    <row r="101" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q100" s="3"/>
+    </row>
+    <row r="101" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -4235,55 +4483,61 @@
       <c r="M101" s="3">
         <v>0</v>
       </c>
-      <c r="N101" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="O101" s="3">
-        <v>0</v>
-      </c>
-      <c r="P101" s="3"/>
-    </row>
-    <row r="102" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="N101" s="3">
+        <v>0</v>
+      </c>
+      <c r="O101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P101" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q101" s="3"/>
+    </row>
+    <row r="102" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>211000</v>
+      </c>
+      <c r="E102" s="3">
         <v>182700</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-215200</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>116400</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-169100</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>184600</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>100300</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-47500</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-5300</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-299600</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-313700</v>
-      </c>
-      <c r="N102" s="3">
-        <v>518600</v>
       </c>
       <c r="O102" s="3">
         <v>518600</v>
       </c>
-      <c r="P102" s="3"/>
+      <c r="P102" s="3">
+        <v>518600</v>
+      </c>
+      <c r="Q102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/AAII_Financials/Yearly/MTB_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/MTB_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="157" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="162" uniqueCount="92">
   <si>
     <t>MTB</t>
   </si>
@@ -2708,25 +2708,25 @@
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>0</v>
+        <v>5843000</v>
       </c>
       <c r="E58" s="3">
-        <v>0</v>
-      </c>
-      <c r="F58" s="3">
-        <v>0</v>
-      </c>
-      <c r="G58" s="3">
-        <v>0</v>
-      </c>
-      <c r="H58" s="3">
-        <v>0</v>
-      </c>
-      <c r="I58" s="3">
-        <v>0</v>
-      </c>
-      <c r="J58" s="3">
-        <v>0</v>
+        <v>4299100</v>
+      </c>
+      <c r="F58" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G58" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H58" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I58" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J58" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K58" s="3">
         <v>0</v>
@@ -2843,10 +2843,10 @@
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>8201000</v>
+        <v>7674000</v>
       </c>
       <c r="E61" s="3">
-        <v>3964500</v>
+        <v>3220400</v>
       </c>
       <c r="F61" s="3">
         <v>3485400</v>

--- a/AAII_Financials/Yearly/MTB_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/MTB_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="162" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="167" uniqueCount="92">
   <si>
     <t>MTB</t>
   </si>
@@ -728,25 +728,25 @@
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>10224000</v>
+        <v>8998000</v>
       </c>
       <c r="E8" s="3">
-        <v>6247100</v>
+        <v>7662000</v>
       </c>
       <c r="F8" s="3">
-        <v>3938800</v>
+        <v>6067000</v>
       </c>
       <c r="G8" s="3">
-        <v>4192700</v>
+        <v>5154800</v>
       </c>
       <c r="H8" s="3">
-        <v>4879600</v>
+        <v>5967900</v>
       </c>
       <c r="I8" s="3">
-        <v>4598700</v>
+        <v>5796300</v>
       </c>
       <c r="J8" s="3">
-        <v>4167800</v>
+        <v>5464200</v>
       </c>
       <c r="K8" s="3">
         <v>3895900</v>
@@ -817,26 +817,26 @@
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="H10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="J10" s="3" t="s">
-        <v>5</v>
+      <c r="D10" s="3">
+        <v>8998000</v>
+      </c>
+      <c r="E10" s="3">
+        <v>7662000</v>
+      </c>
+      <c r="F10" s="3">
+        <v>6067000</v>
+      </c>
+      <c r="G10" s="3">
+        <v>5154800</v>
+      </c>
+      <c r="H10" s="3">
+        <v>5967900</v>
+      </c>
+      <c r="I10" s="3">
+        <v>5796300</v>
+      </c>
+      <c r="J10" s="3">
+        <v>5464200</v>
       </c>
       <c r="K10" s="3" t="s">
         <v>5</v>
@@ -971,26 +971,26 @@
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3">
-        <v>0</v>
+      <c r="D14" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="E14" s="3">
-        <v>0</v>
+        <v>338000</v>
       </c>
       <c r="F14" s="3">
-        <v>0</v>
-      </c>
-      <c r="G14" s="3">
-        <v>0</v>
+        <v>44000</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="H14" s="3">
-        <v>0</v>
+        <v>50000</v>
       </c>
       <c r="I14" s="3">
-        <v>0</v>
-      </c>
-      <c r="J14" s="3">
-        <v>0</v>
+        <v>135000</v>
+      </c>
+      <c r="J14" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K14" s="3">
         <v>0</v>
@@ -1017,25 +1017,25 @@
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>-62000</v>
+        <v>497000</v>
       </c>
       <c r="E15" s="3">
-        <v>-55600</v>
+        <v>435000</v>
       </c>
       <c r="F15" s="3">
-        <v>-10200</v>
+        <v>324000</v>
       </c>
       <c r="G15" s="3">
-        <v>-14900</v>
+        <v>320300</v>
       </c>
       <c r="H15" s="3">
-        <v>-19500</v>
+        <v>301300</v>
       </c>
       <c r="I15" s="3">
-        <v>-24500</v>
+        <v>179000</v>
       </c>
       <c r="J15" s="3">
-        <v>-31400</v>
+        <v>197100</v>
       </c>
       <c r="K15" s="3">
         <v>-42600</v>
@@ -1078,25 +1078,25 @@
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>3754000</v>
+        <v>5002000</v>
       </c>
       <c r="E17" s="3">
-        <v>942200</v>
+        <v>4566000</v>
       </c>
       <c r="F17" s="3">
-        <v>114000</v>
+        <v>3488000</v>
       </c>
       <c r="G17" s="3">
-        <v>326400</v>
+        <v>3316600</v>
       </c>
       <c r="H17" s="3">
-        <v>925300</v>
+        <v>3309700</v>
       </c>
       <c r="I17" s="3">
-        <v>658400</v>
+        <v>3060000</v>
       </c>
       <c r="J17" s="3">
-        <v>554800</v>
+        <v>3007100</v>
       </c>
       <c r="K17" s="3">
         <v>616000</v>
@@ -1123,25 +1123,25 @@
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>6470000</v>
+        <v>3996000</v>
       </c>
       <c r="E18" s="3">
-        <v>5305000</v>
+        <v>3096000</v>
       </c>
       <c r="F18" s="3">
-        <v>3824800</v>
+        <v>2579000</v>
       </c>
       <c r="G18" s="3">
-        <v>3866300</v>
+        <v>1838200</v>
       </c>
       <c r="H18" s="3">
-        <v>3954300</v>
+        <v>2658300</v>
       </c>
       <c r="I18" s="3">
-        <v>3940300</v>
+        <v>2736300</v>
       </c>
       <c r="J18" s="3">
-        <v>3613000</v>
+        <v>2457100</v>
       </c>
       <c r="K18" s="3">
         <v>3279900</v>
@@ -1187,25 +1187,25 @@
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>-2851000</v>
+        <v>377000</v>
       </c>
       <c r="E20" s="3">
-        <v>-2693800</v>
+        <v>146000</v>
       </c>
       <c r="F20" s="3">
-        <v>-1369600</v>
+        <v>80000</v>
       </c>
       <c r="G20" s="3">
-        <v>-2096800</v>
+        <v>68700</v>
       </c>
       <c r="H20" s="3">
-        <v>-1407000</v>
+        <v>61000</v>
       </c>
       <c r="I20" s="3">
-        <v>-1432100</v>
+        <v>93000</v>
       </c>
       <c r="J20" s="3">
-        <v>-1289200</v>
+        <v>133200</v>
       </c>
       <c r="K20" s="3">
         <v>-1221500</v>
@@ -1232,25 +1232,25 @@
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>3985000</v>
+        <v>4116000</v>
       </c>
       <c r="E21" s="3">
-        <v>2948800</v>
+        <v>3385000</v>
       </c>
       <c r="F21" s="3">
-        <v>2689600</v>
+        <v>2823000</v>
       </c>
       <c r="G21" s="3">
-        <v>2005000</v>
+        <v>2089800</v>
       </c>
       <c r="H21" s="3">
-        <v>2776700</v>
+        <v>2898600</v>
       </c>
       <c r="I21" s="3">
-        <v>2637600</v>
+        <v>2822200</v>
       </c>
       <c r="J21" s="3">
-        <v>2464800</v>
+        <v>2521000</v>
       </c>
       <c r="K21" s="3">
         <v>2208000</v>
@@ -1276,26 +1276,26 @@
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D22" s="3">
-        <v>0</v>
-      </c>
-      <c r="E22" s="3">
-        <v>0</v>
-      </c>
-      <c r="F22" s="3">
-        <v>0</v>
-      </c>
-      <c r="G22" s="3">
-        <v>0</v>
-      </c>
-      <c r="H22" s="3">
-        <v>0</v>
-      </c>
-      <c r="I22" s="3">
-        <v>0</v>
-      </c>
-      <c r="J22" s="3">
-        <v>0</v>
+      <c r="D22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J22" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K22" s="3">
         <v>0</v>
@@ -1325,10 +1325,10 @@
         <v>3619000</v>
       </c>
       <c r="E23" s="3">
-        <v>2611100</v>
+        <v>2612000</v>
       </c>
       <c r="F23" s="3">
-        <v>2455100</v>
+        <v>2455000</v>
       </c>
       <c r="G23" s="3">
         <v>1769500</v>
@@ -1370,10 +1370,10 @@
         <v>878000</v>
       </c>
       <c r="E24" s="3">
-        <v>619500</v>
+        <v>620000</v>
       </c>
       <c r="F24" s="3">
-        <v>596400</v>
+        <v>596000</v>
       </c>
       <c r="G24" s="3">
         <v>416400</v>
@@ -1385,7 +1385,7 @@
         <v>590200</v>
       </c>
       <c r="J24" s="3">
-        <v>830100</v>
+        <v>915600</v>
       </c>
       <c r="K24" s="3">
         <v>743300</v>
@@ -1460,10 +1460,10 @@
         <v>2741000</v>
       </c>
       <c r="E26" s="3">
-        <v>1991700</v>
+        <v>1992000</v>
       </c>
       <c r="F26" s="3">
-        <v>1858700</v>
+        <v>1859000</v>
       </c>
       <c r="G26" s="3">
         <v>1353200</v>
@@ -1475,7 +1475,7 @@
         <v>1918100</v>
       </c>
       <c r="J26" s="3">
-        <v>1493700</v>
+        <v>1408300</v>
       </c>
       <c r="K26" s="3">
         <v>1315100</v>
@@ -1505,7 +1505,7 @@
         <v>2636000</v>
       </c>
       <c r="E27" s="3">
-        <v>1891500</v>
+        <v>1891000</v>
       </c>
       <c r="F27" s="3">
         <v>1777000</v>
@@ -1520,7 +1520,7 @@
         <v>1836000</v>
       </c>
       <c r="J27" s="3">
-        <v>1412900</v>
+        <v>1327500</v>
       </c>
       <c r="K27" s="3">
         <v>1223500</v>
@@ -1591,26 +1591,26 @@
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="D29" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E29" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F29" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G29" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="H29" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I29" s="3" t="s">
-        <v>5</v>
+      <c r="D29" s="3">
+        <v>0</v>
+      </c>
+      <c r="E29" s="3">
+        <v>0</v>
+      </c>
+      <c r="F29" s="3">
+        <v>0</v>
+      </c>
+      <c r="G29" s="3">
+        <v>0</v>
+      </c>
+      <c r="H29" s="3">
+        <v>0</v>
+      </c>
+      <c r="I29" s="3">
+        <v>0</v>
       </c>
       <c r="J29" s="3">
-        <v>-85400</v>
+        <v>0</v>
       </c>
       <c r="K29" s="3" t="s">
         <v>5</v>
@@ -1727,25 +1727,25 @@
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>2851000</v>
+        <v>-377000</v>
       </c>
       <c r="E32" s="3">
-        <v>2693800</v>
+        <v>-146000</v>
       </c>
       <c r="F32" s="3">
-        <v>1369600</v>
+        <v>-80000</v>
       </c>
       <c r="G32" s="3">
-        <v>2096800</v>
+        <v>-68700</v>
       </c>
       <c r="H32" s="3">
-        <v>1407000</v>
+        <v>-61000</v>
       </c>
       <c r="I32" s="3">
-        <v>1432100</v>
+        <v>-93000</v>
       </c>
       <c r="J32" s="3">
-        <v>1289200</v>
+        <v>-133200</v>
       </c>
       <c r="K32" s="3">
         <v>1221500</v>
@@ -1772,25 +1772,25 @@
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>2636000</v>
+        <v>2741000</v>
       </c>
       <c r="E33" s="3">
-        <v>1891500</v>
+        <v>1992000</v>
       </c>
       <c r="F33" s="3">
-        <v>1777000</v>
+        <v>1859000</v>
       </c>
       <c r="G33" s="3">
-        <v>1279100</v>
+        <v>1353200</v>
       </c>
       <c r="H33" s="3">
-        <v>1849500</v>
+        <v>1929100</v>
       </c>
       <c r="I33" s="3">
-        <v>1836000</v>
+        <v>1918100</v>
       </c>
       <c r="J33" s="3">
-        <v>1327500</v>
+        <v>1408300</v>
       </c>
       <c r="K33" s="3">
         <v>1223500</v>
@@ -1862,25 +1862,25 @@
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>2636000</v>
+        <v>2741000</v>
       </c>
       <c r="E35" s="3">
-        <v>1891500</v>
+        <v>1992000</v>
       </c>
       <c r="F35" s="3">
-        <v>1777000</v>
+        <v>1859000</v>
       </c>
       <c r="G35" s="3">
-        <v>1279100</v>
+        <v>1353200</v>
       </c>
       <c r="H35" s="3">
-        <v>1849500</v>
+        <v>1929100</v>
       </c>
       <c r="I35" s="3">
-        <v>1836000</v>
+        <v>1918100</v>
       </c>
       <c r="J35" s="3">
-        <v>1327500</v>
+        <v>1408300</v>
       </c>
       <c r="K35" s="3">
         <v>1223500</v>
@@ -1998,7 +1998,7 @@
         <v>1731000</v>
       </c>
       <c r="E41" s="3">
-        <v>1517200</v>
+        <v>1520000</v>
       </c>
       <c r="F41" s="3">
         <v>1337600</v>
@@ -2007,13 +2007,13 @@
         <v>1552700</v>
       </c>
       <c r="H41" s="3">
-        <v>1432800</v>
+        <v>770300</v>
       </c>
       <c r="I41" s="3">
-        <v>1605400</v>
+        <v>921400</v>
       </c>
       <c r="J41" s="3">
-        <v>1420900</v>
+        <v>741500</v>
       </c>
       <c r="K41" s="3">
         <v>1320500</v>
@@ -2040,25 +2040,25 @@
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>29302000</v>
+        <v>28477000</v>
       </c>
       <c r="E42" s="3">
-        <v>26011500</v>
+        <v>25489000</v>
       </c>
       <c r="F42" s="3">
-        <v>42805700</v>
+        <v>42343500</v>
       </c>
       <c r="G42" s="3">
-        <v>25206500</v>
+        <v>24760900</v>
       </c>
       <c r="H42" s="3">
-        <v>8588100</v>
+        <v>7655700</v>
       </c>
       <c r="I42" s="3">
-        <v>9113500</v>
+        <v>8289400</v>
       </c>
       <c r="J42" s="3">
-        <v>5704900</v>
+        <v>5201500</v>
       </c>
       <c r="K42" s="3">
         <v>6064700</v>
@@ -2085,25 +2085,25 @@
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>0</v>
+        <v>68000</v>
       </c>
       <c r="E43" s="3">
-        <v>0</v>
+        <v>74000</v>
       </c>
       <c r="F43" s="3">
-        <v>0</v>
+        <v>68000</v>
       </c>
       <c r="G43" s="3">
-        <v>0</v>
+        <v>67000</v>
       </c>
       <c r="H43" s="3">
-        <v>0</v>
+        <v>62000</v>
       </c>
       <c r="I43" s="3">
-        <v>0</v>
-      </c>
-      <c r="J43" s="3">
-        <v>0</v>
+        <v>56000</v>
+      </c>
+      <c r="J43" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K43" s="3">
         <v>0</v>
@@ -2130,25 +2130,25 @@
         <v>37</v>
       </c>
       <c r="D44" s="3">
-        <v>0</v>
+        <v>39000</v>
       </c>
       <c r="E44" s="3">
-        <v>0</v>
+        <v>41000</v>
       </c>
       <c r="F44" s="3">
-        <v>0</v>
+        <v>23900</v>
       </c>
       <c r="G44" s="3">
-        <v>0</v>
+        <v>34700</v>
       </c>
       <c r="H44" s="3">
-        <v>0</v>
+        <v>85600</v>
       </c>
       <c r="I44" s="3">
-        <v>0</v>
+        <v>78400</v>
       </c>
       <c r="J44" s="3">
-        <v>0</v>
+        <v>111900</v>
       </c>
       <c r="K44" s="3">
         <v>0</v>
@@ -2175,25 +2175,25 @@
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>0</v>
+        <v>808000</v>
       </c>
       <c r="E45" s="3">
-        <v>0</v>
+        <v>669000</v>
       </c>
       <c r="F45" s="3">
-        <v>0</v>
+        <v>356200</v>
       </c>
       <c r="G45" s="3">
-        <v>0</v>
+        <v>440900</v>
       </c>
       <c r="H45" s="3">
-        <v>0</v>
+        <v>354100</v>
       </c>
       <c r="I45" s="3">
-        <v>0</v>
+        <v>375000</v>
       </c>
       <c r="J45" s="3">
-        <v>0</v>
+        <v>350200</v>
       </c>
       <c r="K45" s="3">
         <v>0</v>
@@ -2220,25 +2220,25 @@
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>0</v>
+        <v>31502000</v>
       </c>
       <c r="E46" s="3">
-        <v>0</v>
+        <v>27956000</v>
       </c>
       <c r="F46" s="3">
-        <v>0</v>
+        <v>45028100</v>
       </c>
       <c r="G46" s="3">
-        <v>0</v>
+        <v>27911200</v>
       </c>
       <c r="H46" s="3">
-        <v>0</v>
+        <v>10035800</v>
       </c>
       <c r="I46" s="3">
-        <v>0</v>
+        <v>10956200</v>
       </c>
       <c r="J46" s="3">
-        <v>0</v>
+        <v>7462500</v>
       </c>
       <c r="K46" s="3">
         <v>0</v>
@@ -2265,25 +2265,25 @@
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>0</v>
+        <v>26897000</v>
       </c>
       <c r="E47" s="3">
-        <v>0</v>
+        <v>25211000</v>
       </c>
       <c r="F47" s="3">
-        <v>0</v>
+        <v>7155900</v>
       </c>
       <c r="G47" s="3">
-        <v>0</v>
+        <v>7045700</v>
       </c>
       <c r="H47" s="3">
-        <v>0</v>
+        <v>9497300</v>
       </c>
       <c r="I47" s="3">
-        <v>0</v>
+        <v>12692800</v>
       </c>
       <c r="J47" s="3">
-        <v>0</v>
+        <v>14664500</v>
       </c>
       <c r="K47" s="3">
         <v>0</v>
@@ -2313,7 +2313,7 @@
         <v>1739000</v>
       </c>
       <c r="E48" s="3">
-        <v>1653600</v>
+        <v>1654000</v>
       </c>
       <c r="F48" s="3">
         <v>1144800</v>
@@ -2355,25 +2355,25 @@
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>8612000</v>
+        <v>9262000</v>
       </c>
       <c r="E49" s="3">
-        <v>8699500</v>
+        <v>8948000</v>
       </c>
       <c r="F49" s="3">
-        <v>4597100</v>
+        <v>4946800</v>
       </c>
       <c r="G49" s="3">
-        <v>4607300</v>
+        <v>4941900</v>
       </c>
       <c r="H49" s="3">
-        <v>4622100</v>
+        <v>4990200</v>
       </c>
       <c r="I49" s="3">
-        <v>4640200</v>
+        <v>4875400</v>
       </c>
       <c r="J49" s="3">
-        <v>4664700</v>
+        <v>4893800</v>
       </c>
       <c r="K49" s="3">
         <v>4690800</v>
@@ -2490,25 +2490,25 @@
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>0</v>
+        <v>7304000</v>
       </c>
       <c r="E52" s="3">
-        <v>0</v>
+        <v>7485000</v>
       </c>
       <c r="F52" s="3">
-        <v>0</v>
+        <v>6287400</v>
       </c>
       <c r="G52" s="3">
-        <v>0</v>
+        <v>5796300</v>
       </c>
       <c r="H52" s="3">
-        <v>0</v>
+        <v>4778700</v>
       </c>
       <c r="I52" s="3">
-        <v>0</v>
+        <v>4030600</v>
       </c>
       <c r="J52" s="3">
-        <v>0</v>
+        <v>4332500</v>
       </c>
       <c r="K52" s="3">
         <v>0</v>
@@ -2586,19 +2586,19 @@
         <v>200730000</v>
       </c>
       <c r="F54" s="3">
-        <v>155107000</v>
+        <v>155107200</v>
       </c>
       <c r="G54" s="3">
-        <v>142601000</v>
+        <v>142601100</v>
       </c>
       <c r="H54" s="3">
-        <v>119873000</v>
+        <v>119872800</v>
       </c>
       <c r="I54" s="3">
-        <v>120097000</v>
+        <v>120097400</v>
       </c>
       <c r="J54" s="3">
-        <v>118594000</v>
+        <v>118593500</v>
       </c>
       <c r="K54" s="3">
         <v>123449000</v>
@@ -2663,25 +2663,25 @@
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>3799000</v>
+        <v>163274000</v>
       </c>
       <c r="E57" s="3">
-        <v>3668500</v>
+        <v>163515000</v>
       </c>
       <c r="F57" s="3">
-        <v>1696900</v>
+        <v>131543400</v>
       </c>
       <c r="G57" s="3">
-        <v>1699400</v>
+        <v>119805700</v>
       </c>
       <c r="H57" s="3">
-        <v>1762800</v>
+        <v>94770100</v>
       </c>
       <c r="I57" s="3">
-        <v>1446700</v>
+        <v>90156600</v>
       </c>
       <c r="J57" s="3">
-        <v>1454800</v>
+        <v>92432100</v>
       </c>
       <c r="K57" s="3">
         <v>1634600</v>
@@ -2708,25 +2708,25 @@
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>5843000</v>
+        <v>6898000</v>
       </c>
       <c r="E58" s="3">
-        <v>4299100</v>
-      </c>
-      <c r="F58" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G58" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="H58" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I58" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="J58" s="3" t="s">
-        <v>5</v>
+        <v>5654000</v>
+      </c>
+      <c r="F58" s="3">
+        <v>1044800</v>
+      </c>
+      <c r="G58" s="3">
+        <v>1050000</v>
+      </c>
+      <c r="H58" s="3">
+        <v>2057900</v>
+      </c>
+      <c r="I58" s="3">
+        <v>5234900</v>
+      </c>
+      <c r="J58" s="3">
+        <v>1014200</v>
       </c>
       <c r="K58" s="3">
         <v>0</v>
@@ -2752,20 +2752,20 @@
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="D59" s="3">
-        <v>717000</v>
-      </c>
-      <c r="E59" s="3">
-        <v>709000</v>
-      </c>
-      <c r="F59" s="3">
-        <v>431000</v>
-      </c>
-      <c r="G59" s="3">
-        <v>467000</v>
-      </c>
-      <c r="H59" s="3">
-        <v>487600</v>
+      <c r="D59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H59" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="I59" s="3" t="s">
         <v>5</v>
@@ -2798,25 +2798,25 @@
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>0</v>
+        <v>170654000</v>
       </c>
       <c r="E60" s="3">
-        <v>0</v>
+        <v>169250000</v>
       </c>
       <c r="F60" s="3">
-        <v>0</v>
+        <v>132629000</v>
       </c>
       <c r="G60" s="3">
-        <v>0</v>
+        <v>120915600</v>
       </c>
       <c r="H60" s="3">
-        <v>0</v>
+        <v>96933400</v>
       </c>
       <c r="I60" s="3">
-        <v>0</v>
+        <v>95486700</v>
       </c>
       <c r="J60" s="3">
-        <v>0</v>
+        <v>93522000</v>
       </c>
       <c r="K60" s="3">
         <v>0</v>
@@ -2843,25 +2843,25 @@
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>7674000</v>
+        <v>8279000</v>
       </c>
       <c r="E61" s="3">
-        <v>3220400</v>
+        <v>3930000</v>
       </c>
       <c r="F61" s="3">
-        <v>3485400</v>
+        <v>3012500</v>
       </c>
       <c r="G61" s="3">
-        <v>4382200</v>
+        <v>3999200</v>
       </c>
       <c r="H61" s="3">
-        <v>6986200</v>
+        <v>5565700</v>
       </c>
       <c r="I61" s="3">
-        <v>8444900</v>
+        <v>7799100</v>
       </c>
       <c r="J61" s="3">
-        <v>8141400</v>
+        <v>7441500</v>
       </c>
       <c r="K61" s="3">
         <v>9493800</v>
@@ -2888,25 +2888,25 @@
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>0</v>
+        <v>2320000</v>
       </c>
       <c r="E62" s="3">
-        <v>0</v>
+        <v>2184000</v>
       </c>
       <c r="F62" s="3">
-        <v>0</v>
+        <v>1517200</v>
       </c>
       <c r="G62" s="3">
-        <v>0</v>
+        <v>1457000</v>
       </c>
       <c r="H62" s="3">
-        <v>0</v>
+        <v>1614000</v>
       </c>
       <c r="I62" s="3">
-        <v>0</v>
+        <v>1308400</v>
       </c>
       <c r="J62" s="3">
-        <v>0</v>
+        <v>1379200</v>
       </c>
       <c r="K62" s="3">
         <v>0</v>
@@ -3074,19 +3074,19 @@
         <v>175412000</v>
       </c>
       <c r="F66" s="3">
-        <v>137204000</v>
+        <v>137203800</v>
       </c>
       <c r="G66" s="3">
-        <v>126414000</v>
+        <v>126413800</v>
       </c>
       <c r="H66" s="3">
-        <v>104156000</v>
+        <v>104156100</v>
       </c>
       <c r="I66" s="3">
-        <v>104637000</v>
+        <v>104637200</v>
       </c>
       <c r="J66" s="3">
-        <v>102343000</v>
+        <v>102342700</v>
       </c>
       <c r="K66" s="3">
         <v>106963000</v>
@@ -3225,7 +3225,7 @@
         <v>2011000</v>
       </c>
       <c r="E70" s="3">
-        <v>2010600</v>
+        <v>2011000</v>
       </c>
       <c r="F70" s="3">
         <v>1750000</v>
@@ -3495,7 +3495,7 @@
         <v>24946000</v>
       </c>
       <c r="E76" s="3">
-        <v>23307400</v>
+        <v>23307000</v>
       </c>
       <c r="F76" s="3">
         <v>16153400</v>
@@ -3632,25 +3632,25 @@
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>2636000</v>
+        <v>2741000</v>
       </c>
       <c r="E81" s="3">
-        <v>1891500</v>
+        <v>1992000</v>
       </c>
       <c r="F81" s="3">
-        <v>1777000</v>
+        <v>1859000</v>
       </c>
       <c r="G81" s="3">
-        <v>1279100</v>
+        <v>1353200</v>
       </c>
       <c r="H81" s="3">
-        <v>1849500</v>
+        <v>1929100</v>
       </c>
       <c r="I81" s="3">
-        <v>1836000</v>
+        <v>1918100</v>
       </c>
       <c r="J81" s="3">
-        <v>1327500</v>
+        <v>1408300</v>
       </c>
       <c r="K81" s="3">
         <v>1223500</v>
@@ -3696,25 +3696,25 @@
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>366000</v>
+        <v>304000</v>
       </c>
       <c r="E83" s="3">
-        <v>337700</v>
+        <v>282000</v>
       </c>
       <c r="F83" s="3">
-        <v>234400</v>
+        <v>224000</v>
       </c>
       <c r="G83" s="3">
-        <v>235500</v>
+        <v>220600</v>
       </c>
       <c r="H83" s="3">
-        <v>229400</v>
+        <v>209900</v>
       </c>
       <c r="I83" s="3">
-        <v>129400</v>
+        <v>104900</v>
       </c>
       <c r="J83" s="3">
-        <v>141000</v>
+        <v>109600</v>
       </c>
       <c r="K83" s="3">
         <v>149600</v>
@@ -3969,7 +3969,7 @@
         <v>3905000</v>
       </c>
       <c r="E89" s="3">
-        <v>4573700</v>
+        <v>4574000</v>
       </c>
       <c r="F89" s="3">
         <v>2715000</v>
@@ -4033,10 +4033,10 @@
         <v>-256000</v>
       </c>
       <c r="E91" s="3">
-        <v>-214400</v>
+        <v>-214000</v>
       </c>
       <c r="F91" s="3">
-        <v>-149200</v>
+        <v>-149000</v>
       </c>
       <c r="G91" s="3">
         <v>-172300</v>
@@ -4168,10 +4168,10 @@
         <v>-7874000</v>
       </c>
       <c r="E94" s="3">
-        <v>16592700</v>
+        <v>16592000</v>
       </c>
       <c r="F94" s="3">
-        <v>-13631600</v>
+        <v>-13631000</v>
       </c>
       <c r="G94" s="3">
         <v>-22020500</v>
@@ -4229,25 +4229,25 @@
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>-968000</v>
+        <v>868000</v>
       </c>
       <c r="E96" s="3">
-        <v>-881000</v>
+        <v>784000</v>
       </c>
       <c r="F96" s="3">
-        <v>-648500</v>
+        <v>580000</v>
       </c>
       <c r="G96" s="3">
-        <v>-636400</v>
+        <v>568100</v>
       </c>
       <c r="H96" s="3">
-        <v>-619600</v>
+        <v>552100</v>
       </c>
       <c r="I96" s="3">
-        <v>-582900</v>
+        <v>510400</v>
       </c>
       <c r="J96" s="3">
-        <v>-530100</v>
+        <v>457400</v>
       </c>
       <c r="K96" s="3">
         <v>-523200</v>
@@ -4412,10 +4412,10 @@
         <v>4180000</v>
       </c>
       <c r="E100" s="3">
-        <v>-20983800</v>
+        <v>-20984000</v>
       </c>
       <c r="F100" s="3">
-        <v>10701500</v>
+        <v>10701000</v>
       </c>
       <c r="G100" s="3">
         <v>21347700</v>
@@ -4453,26 +4453,26 @@
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="D101" s="3">
-        <v>0</v>
-      </c>
-      <c r="E101" s="3">
-        <v>0</v>
-      </c>
-      <c r="F101" s="3">
-        <v>0</v>
-      </c>
-      <c r="G101" s="3">
-        <v>0</v>
-      </c>
-      <c r="H101" s="3">
-        <v>0</v>
-      </c>
-      <c r="I101" s="3">
-        <v>0</v>
-      </c>
-      <c r="J101" s="3">
-        <v>0</v>
+      <c r="D101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J101" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K101" s="3">
         <v>0</v>
@@ -4502,10 +4502,10 @@
         <v>211000</v>
       </c>
       <c r="E102" s="3">
-        <v>182700</v>
+        <v>182000</v>
       </c>
       <c r="F102" s="3">
-        <v>-215200</v>
+        <v>-215000</v>
       </c>
       <c r="G102" s="3">
         <v>116400</v>

--- a/AAII_Financials/Yearly/MTB_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/MTB_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="167" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="172" uniqueCount="92">
   <si>
     <t>MTB</t>
   </si>
@@ -656,119 +656,125 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:Q102"/>
+  <dimension ref="A5:R102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="12" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="13" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E7" s="2">
         <v>45291</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>44926</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44561</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44196</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>43830</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>43465</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>43100</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>42735</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>42369</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>42004</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>41639</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>41274</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>40908</v>
       </c>
-      <c r="Q7" s="2"/>
-    </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R7" s="2"/>
+    </row>
+    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>8669000</v>
+      </c>
+      <c r="E8" s="3">
         <v>8998000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>7662000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>6067000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>5154800</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>5967900</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>5796300</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>5464200</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>3895900</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>3170800</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>2956900</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>2957300</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>2941700</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>2792100</v>
       </c>
-      <c r="Q8" s="3"/>
-    </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R8" s="3"/>
+    </row>
+    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
@@ -811,36 +817,39 @@
       <c r="P9" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q9" s="3"/>
-    </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R9" s="3"/>
+    </row>
+    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>8669000</v>
+      </c>
+      <c r="E10" s="3">
         <v>8998000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>7662000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>6067000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>5154800</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>5967900</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>5796300</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>5464200</v>
       </c>
-      <c r="K10" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="L10" s="3" t="s">
         <v>5</v>
       </c>
@@ -856,9 +865,12 @@
       <c r="P10" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q10" s="3"/>
-    </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R10" s="3"/>
+    </row>
+    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -876,8 +888,9 @@
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
-    </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R11" s="3"/>
+    </row>
+    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -920,9 +933,12 @@
       <c r="P12" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q12" s="3"/>
-    </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q12" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R12" s="3"/>
+    </row>
+    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -965,35 +981,38 @@
       <c r="P13" s="3">
         <v>0</v>
       </c>
-      <c r="Q13" s="3"/>
-    </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q13" s="3">
+        <v>0</v>
+      </c>
+      <c r="R13" s="3"/>
+    </row>
+    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E14" s="3">
+      <c r="D14" s="3">
+        <v>27000</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F14" s="3">
         <v>338000</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>44000</v>
       </c>
-      <c r="G14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="H14" s="3">
+      <c r="H14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I14" s="3">
         <v>50000</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>135000</v>
       </c>
-      <c r="J14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="K14" s="3">
-        <v>0</v>
+      <c r="K14" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="L14" s="3">
         <v>0</v>
@@ -1010,54 +1029,60 @@
       <c r="P14" s="3">
         <v>0</v>
       </c>
-      <c r="Q14" s="3"/>
-    </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q14" s="3">
+        <v>0</v>
+      </c>
+      <c r="R14" s="3"/>
+    </row>
+    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>508000</v>
+      </c>
+      <c r="E15" s="3">
         <v>497000</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>435000</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>324000</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>320300</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>301300</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>179000</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>197100</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>-42600</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>-26400</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>-33800</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>-46900</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>-60600</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>-61600</v>
       </c>
-      <c r="Q15" s="3"/>
-    </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R15" s="3"/>
+    </row>
+    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1072,98 +1097,105 @@
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
-    </row>
-    <row r="17" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R16" s="3"/>
+    </row>
+    <row r="17" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>5133000</v>
+      </c>
+      <c r="E17" s="3">
         <v>5002000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>4566000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>3488000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>3316600</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>3309700</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>3060000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>3007100</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>616000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>498300</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>404400</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>469100</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>547200</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>672300</v>
       </c>
-      <c r="Q17" s="3"/>
-    </row>
-    <row r="18" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R17" s="3"/>
+    </row>
+    <row r="18" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>3536000</v>
+      </c>
+      <c r="E18" s="3">
         <v>3996000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>3096000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>2579000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>1838200</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>2658300</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>2736300</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>2457100</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>3279900</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>2672600</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>2552400</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>2488200</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>2394500</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>2119800</v>
       </c>
-      <c r="Q18" s="3"/>
-    </row>
-    <row r="19" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R18" s="3"/>
+    </row>
+    <row r="19" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1181,98 +1213,105 @@
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
       <c r="Q19" s="3"/>
-    </row>
-    <row r="20" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R19" s="3"/>
+    </row>
+    <row r="20" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>199000</v>
+      </c>
+      <c r="E20" s="3">
         <v>377000</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>146000</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>80000</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>68700</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>61000</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>93000</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>133200</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-1221500</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-997900</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-910200</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-770700</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-842000</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-895200</v>
       </c>
-      <c r="Q20" s="3"/>
-    </row>
-    <row r="21" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R20" s="3"/>
+    </row>
+    <row r="21" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>3845000</v>
+      </c>
+      <c r="E21" s="3">
         <v>4116000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>3385000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>2823000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>2089800</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>2898600</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>2822200</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>2521000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>2208000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>1800100</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>1772600</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>1855900</v>
       </c>
-      <c r="O21" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P21" s="3">
+      <c r="P21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q21" s="3">
         <v>1366500</v>
       </c>
-      <c r="Q21" s="3"/>
-    </row>
-    <row r="22" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R21" s="3"/>
+    </row>
+    <row r="22" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1297,8 +1336,8 @@
       <c r="J22" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K22" s="3">
-        <v>0</v>
+      <c r="K22" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="L22" s="3">
         <v>0</v>
@@ -1315,99 +1354,108 @@
       <c r="P22" s="3">
         <v>0</v>
       </c>
-      <c r="Q22" s="3"/>
-    </row>
-    <row r="23" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q22" s="3">
+        <v>0</v>
+      </c>
+      <c r="R22" s="3"/>
+    </row>
+    <row r="23" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>3310000</v>
+      </c>
+      <c r="E23" s="3">
         <v>3619000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>2612000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>2455000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>1769500</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>2547300</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>2508200</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>2323900</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>2058400</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>1674700</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>1642200</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>1717500</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>1552500</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>1224600</v>
       </c>
-      <c r="Q23" s="3"/>
-    </row>
-    <row r="24" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R23" s="3"/>
+    </row>
+    <row r="24" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>722000</v>
+      </c>
+      <c r="E24" s="3">
         <v>878000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>620000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>596000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>416400</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>618100</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>590200</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>915600</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>743300</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>595000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>576000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>579100</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>523000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>365100</v>
       </c>
-      <c r="Q24" s="3"/>
-    </row>
-    <row r="25" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R24" s="3"/>
+    </row>
+    <row r="25" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1450,99 +1498,108 @@
       <c r="P25" s="3">
         <v>0</v>
       </c>
-      <c r="Q25" s="3"/>
-    </row>
-    <row r="26" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q25" s="3">
+        <v>0</v>
+      </c>
+      <c r="R25" s="3"/>
+    </row>
+    <row r="26" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>2588000</v>
+      </c>
+      <c r="E26" s="3">
         <v>2741000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>1992000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>1859000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>1353200</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>1929100</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>1918100</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>1408300</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>1315100</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>1079700</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>1066200</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>1138500</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>1029500</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>859500</v>
       </c>
-      <c r="Q26" s="3"/>
-    </row>
-    <row r="27" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R26" s="3"/>
+    </row>
+    <row r="27" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>2449000</v>
+      </c>
+      <c r="E27" s="3">
         <v>2636000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>1891000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>1777000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>1279100</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>1849500</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>1836000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>1327500</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>1223500</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>987700</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>978500</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>1062400</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>953400</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>781700</v>
       </c>
-      <c r="Q27" s="3"/>
-    </row>
-    <row r="28" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R27" s="3"/>
+    </row>
+    <row r="28" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1585,9 +1642,12 @@
       <c r="P28" s="3">
         <v>0</v>
       </c>
-      <c r="Q28" s="3"/>
-    </row>
-    <row r="29" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q28" s="3">
+        <v>0</v>
+      </c>
+      <c r="R28" s="3"/>
+    </row>
+    <row r="29" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1612,8 +1672,8 @@
       <c r="J29" s="3">
         <v>0</v>
       </c>
-      <c r="K29" s="3" t="s">
-        <v>5</v>
+      <c r="K29" s="3">
+        <v>0</v>
       </c>
       <c r="L29" s="3" t="s">
         <v>5</v>
@@ -1630,9 +1690,12 @@
       <c r="P29" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q29" s="3"/>
-    </row>
-    <row r="30" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R29" s="3"/>
+    </row>
+    <row r="30" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1675,9 +1738,12 @@
       <c r="P30" s="3">
         <v>0</v>
       </c>
-      <c r="Q30" s="3"/>
-    </row>
-    <row r="31" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q30" s="3">
+        <v>0</v>
+      </c>
+      <c r="R30" s="3"/>
+    </row>
+    <row r="31" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1720,99 +1786,108 @@
       <c r="P31" s="3">
         <v>0</v>
       </c>
-      <c r="Q31" s="3"/>
-    </row>
-    <row r="32" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q31" s="3">
+        <v>0</v>
+      </c>
+      <c r="R31" s="3"/>
+    </row>
+    <row r="32" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-199000</v>
+      </c>
+      <c r="E32" s="3">
         <v>-377000</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-146000</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-80000</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-68700</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-61000</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-93000</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-133200</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>1221500</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>997900</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>910200</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>770700</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>842000</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>895200</v>
       </c>
-      <c r="Q32" s="3"/>
-    </row>
-    <row r="33" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R32" s="3"/>
+    </row>
+    <row r="33" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>2588000</v>
+      </c>
+      <c r="E33" s="3">
         <v>2741000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>1992000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>1859000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>1353200</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>1929100</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>1918100</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>1408300</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>1223500</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>987700</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>978500</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>1062400</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>953400</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>781700</v>
       </c>
-      <c r="Q33" s="3"/>
-    </row>
-    <row r="34" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R33" s="3"/>
+    </row>
+    <row r="34" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1855,104 +1930,113 @@
       <c r="P34" s="3">
         <v>0</v>
       </c>
-      <c r="Q34" s="3"/>
-    </row>
-    <row r="35" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q34" s="3">
+        <v>0</v>
+      </c>
+      <c r="R34" s="3"/>
+    </row>
+    <row r="35" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>2588000</v>
+      </c>
+      <c r="E35" s="3">
         <v>2741000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>1992000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>1859000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>1353200</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>1929100</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>1918100</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>1408300</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>1223500</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>987700</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>978500</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>1062400</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>953400</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>781700</v>
       </c>
-      <c r="Q35" s="3"/>
-    </row>
-    <row r="37" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R35" s="3"/>
+    </row>
+    <row r="37" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E38" s="2">
         <v>45291</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>44926</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44561</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44196</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>43830</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>43465</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>43100</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>42735</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>42369</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>42004</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>41639</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>41274</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>40908</v>
       </c>
-      <c r="Q38" s="2"/>
-    </row>
-    <row r="39" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R38" s="2"/>
+    </row>
+    <row r="39" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1970,8 +2054,9 @@
       <c r="O39" s="3"/>
       <c r="P39" s="3"/>
       <c r="Q39" s="3"/>
-    </row>
-    <row r="40" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R39" s="3"/>
+    </row>
+    <row r="40" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1989,124 +2074,131 @@
       <c r="O40" s="3"/>
       <c r="P40" s="3"/>
       <c r="Q40" s="3"/>
-    </row>
-    <row r="41" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R40" s="3"/>
+    </row>
+    <row r="41" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>1909000</v>
+      </c>
+      <c r="E41" s="3">
         <v>1731000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>1520000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>1337600</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>1552700</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>770300</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>921400</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>741500</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>1320500</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>1368000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>1290000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>1573400</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>1983600</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>1449500</v>
       </c>
-      <c r="Q41" s="3"/>
-    </row>
-    <row r="42" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R41" s="3"/>
+    </row>
+    <row r="42" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>19207000</v>
+      </c>
+      <c r="E42" s="3">
         <v>28477000</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>25489000</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>42343500</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>24760900</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>7655700</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>8289400</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>5201500</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>6064700</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>8672000</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>7481500</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>2816200</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>924600</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>1086500</v>
       </c>
-      <c r="Q42" s="3"/>
-    </row>
-    <row r="43" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R42" s="3"/>
+    </row>
+    <row r="43" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>72000</v>
+      </c>
+      <c r="E43" s="3">
         <v>68000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>74000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>68000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>67000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>62000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>56000</v>
       </c>
-      <c r="J43" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="K43" s="3">
-        <v>0</v>
+      <c r="K43" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="L43" s="3">
         <v>0</v>
@@ -2123,36 +2215,39 @@
       <c r="P43" s="3">
         <v>0</v>
       </c>
-      <c r="Q43" s="3"/>
-    </row>
-    <row r="44" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q43" s="3">
+        <v>0</v>
+      </c>
+      <c r="R43" s="3"/>
+    </row>
+    <row r="44" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>35000</v>
+      </c>
+      <c r="E44" s="3">
         <v>39000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>41000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>23900</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>34700</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>85600</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>78400</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>111900</v>
       </c>
-      <c r="K44" s="3">
-        <v>0</v>
-      </c>
       <c r="L44" s="3">
         <v>0</v>
       </c>
@@ -2168,36 +2263,39 @@
       <c r="P44" s="3">
         <v>0</v>
       </c>
-      <c r="Q44" s="3"/>
-    </row>
-    <row r="45" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q44" s="3">
+        <v>0</v>
+      </c>
+      <c r="R44" s="3"/>
+    </row>
+    <row r="45" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>22000</v>
+      </c>
+      <c r="E45" s="3">
         <v>808000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>669000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>356200</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>440900</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>354100</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>375000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>350200</v>
       </c>
-      <c r="K45" s="3">
-        <v>0</v>
-      </c>
       <c r="L45" s="3">
         <v>0</v>
       </c>
@@ -2213,36 +2311,39 @@
       <c r="P45" s="3">
         <v>0</v>
       </c>
-      <c r="Q45" s="3"/>
-    </row>
-    <row r="46" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q45" s="3">
+        <v>0</v>
+      </c>
+      <c r="R45" s="3"/>
+    </row>
+    <row r="46" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>31502000</v>
+        <v>21245000</v>
       </c>
       <c r="E46" s="3">
+        <v>31123000</v>
+      </c>
+      <c r="F46" s="3">
         <v>27956000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>45028100</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>27911200</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>10035800</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>10956200</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>7462500</v>
       </c>
-      <c r="K46" s="3">
-        <v>0</v>
-      </c>
       <c r="L46" s="3">
         <v>0</v>
       </c>
@@ -2258,36 +2359,39 @@
       <c r="P46" s="3">
         <v>0</v>
       </c>
-      <c r="Q46" s="3"/>
-    </row>
-    <row r="47" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q46" s="3">
+        <v>0</v>
+      </c>
+      <c r="R46" s="3"/>
+    </row>
+    <row r="47" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>34051000</v>
+      </c>
+      <c r="E47" s="3">
         <v>26897000</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>25211000</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>7155900</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>7045700</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>9497300</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>12692800</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>14664500</v>
       </c>
-      <c r="K47" s="3">
-        <v>0</v>
-      </c>
       <c r="L47" s="3">
         <v>0</v>
       </c>
@@ -2303,99 +2407,108 @@
       <c r="P47" s="3">
         <v>0</v>
       </c>
-      <c r="Q47" s="3"/>
-    </row>
-    <row r="48" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q47" s="3">
+        <v>0</v>
+      </c>
+      <c r="R47" s="3"/>
+    </row>
+    <row r="48" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>1705000</v>
+      </c>
+      <c r="E48" s="3">
         <v>1739000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>1654000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>1144800</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>1161600</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>1140900</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>647400</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>646500</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>675300</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>666700</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>613000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>633500</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>594700</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>581400</v>
       </c>
-      <c r="Q48" s="3"/>
-    </row>
-    <row r="49" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R48" s="3"/>
+    </row>
+    <row r="49" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>9383000</v>
+      </c>
+      <c r="E49" s="3">
         <v>9262000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>8948000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>4946800</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>4941900</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>4990200</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>4875400</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>4893800</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>4690800</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>4733400</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>3559700</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>3593500</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>3640400</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>3701000</v>
       </c>
-      <c r="Q49" s="3"/>
-    </row>
-    <row r="50" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R49" s="3"/>
+    </row>
+    <row r="50" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2438,9 +2551,12 @@
       <c r="P50" s="3">
         <v>0</v>
       </c>
-      <c r="Q50" s="3"/>
-    </row>
-    <row r="51" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q50" s="3">
+        <v>0</v>
+      </c>
+      <c r="R50" s="3"/>
+    </row>
+    <row r="51" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2483,36 +2599,39 @@
       <c r="P51" s="3">
         <v>0</v>
       </c>
-      <c r="Q51" s="3"/>
-    </row>
-    <row r="52" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q51" s="3">
+        <v>0</v>
+      </c>
+      <c r="R51" s="3"/>
+    </row>
+    <row r="52" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>8324000</v>
+      </c>
+      <c r="E52" s="3">
         <v>7304000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>7485000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>6287400</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>5796300</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>4778700</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>4030600</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>4332500</v>
       </c>
-      <c r="K52" s="3">
-        <v>0</v>
-      </c>
       <c r="L52" s="3">
         <v>0</v>
       </c>
@@ -2528,9 +2647,12 @@
       <c r="P52" s="3">
         <v>0</v>
       </c>
-      <c r="Q52" s="3"/>
-    </row>
-    <row r="53" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q52" s="3">
+        <v>0</v>
+      </c>
+      <c r="R52" s="3"/>
+    </row>
+    <row r="53" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2573,54 +2695,60 @@
       <c r="P53" s="3">
         <v>0</v>
       </c>
-      <c r="Q53" s="3"/>
-    </row>
-    <row r="54" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q53" s="3">
+        <v>0</v>
+      </c>
+      <c r="R53" s="3"/>
+    </row>
+    <row r="54" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>208105000</v>
+      </c>
+      <c r="E54" s="3">
         <v>208264000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>200730000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>155107200</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>142601100</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>119872800</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>120097400</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>118593500</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>123449000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>122788000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>96685500</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>85162400</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>83008800</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>77924300</v>
       </c>
-      <c r="Q54" s="3"/>
-    </row>
-    <row r="55" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R54" s="3"/>
+    </row>
+    <row r="55" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2638,8 +2766,9 @@
       <c r="O55" s="3"/>
       <c r="P55" s="3"/>
       <c r="Q55" s="3"/>
-    </row>
-    <row r="56" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R55" s="3"/>
+    </row>
+    <row r="56" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2657,80 +2786,84 @@
       <c r="O56" s="3"/>
       <c r="P56" s="3"/>
       <c r="Q56" s="3"/>
-    </row>
-    <row r="57" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R56" s="3"/>
+    </row>
+    <row r="57" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>161095000</v>
+      </c>
+      <c r="E57" s="3">
         <v>163274000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>163515000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>131543400</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>119805700</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>94770100</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>90156600</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>92432100</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>1634600</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>1708100</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>1355900</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>1114700</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>1512700</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>1790100</v>
       </c>
-      <c r="Q57" s="3"/>
-    </row>
-    <row r="58" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R57" s="3"/>
+    </row>
+    <row r="58" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>6898000</v>
+        <v>2042000</v>
       </c>
       <c r="E58" s="3">
+        <v>6259000</v>
+      </c>
+      <c r="F58" s="3">
         <v>5654000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>1044800</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>1050000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>2057900</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>5234900</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>1014200</v>
       </c>
-      <c r="K58" s="3">
-        <v>0</v>
-      </c>
       <c r="L58" s="3">
         <v>0</v>
       </c>
@@ -2746,9 +2879,12 @@
       <c r="P58" s="3">
         <v>0</v>
       </c>
-      <c r="Q58" s="3"/>
-    </row>
-    <row r="59" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q58" s="3">
+        <v>0</v>
+      </c>
+      <c r="R58" s="3"/>
+    </row>
+    <row r="59" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
@@ -2785,42 +2921,45 @@
       <c r="N59" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="O59" s="3">
-        <v>0</v>
+      <c r="O59" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="P59" s="3">
         <v>0</v>
       </c>
-      <c r="Q59" s="3"/>
-    </row>
-    <row r="60" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q59" s="3">
+        <v>0</v>
+      </c>
+      <c r="R59" s="3"/>
+    </row>
+    <row r="60" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>170654000</v>
+        <v>163137000</v>
       </c>
       <c r="E60" s="3">
+        <v>169533000</v>
+      </c>
+      <c r="F60" s="3">
         <v>169250000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>132629000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>120915600</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>96933400</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>95486700</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>93522000</v>
       </c>
-      <c r="K60" s="3">
-        <v>0</v>
-      </c>
       <c r="L60" s="3">
         <v>0</v>
       </c>
@@ -2836,81 +2975,87 @@
       <c r="P60" s="3">
         <v>0</v>
       </c>
-      <c r="Q60" s="3"/>
-    </row>
-    <row r="61" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q60" s="3">
+        <v>0</v>
+      </c>
+      <c r="R60" s="3"/>
+    </row>
+    <row r="61" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>8279000</v>
+        <v>13122000</v>
       </c>
       <c r="E61" s="3">
+        <v>8918000</v>
+      </c>
+      <c r="F61" s="3">
         <v>3930000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>3012500</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>3999200</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>5565700</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>7799100</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>7441500</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>9493800</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>10653900</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>9007000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>5108900</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>3177700</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>3887800</v>
       </c>
-      <c r="Q61" s="3"/>
-    </row>
-    <row r="62" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R61" s="3"/>
+    </row>
+    <row r="62" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>2320000</v>
+        <v>2762000</v>
       </c>
       <c r="E62" s="3">
+        <v>2802000</v>
+      </c>
+      <c r="F62" s="3">
         <v>2184000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>1517200</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>1457000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>1614000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>1308400</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>1379200</v>
       </c>
-      <c r="K62" s="3">
-        <v>0</v>
-      </c>
       <c r="L62" s="3">
         <v>0</v>
       </c>
@@ -2926,9 +3071,12 @@
       <c r="P62" s="3">
         <v>0</v>
       </c>
-      <c r="Q62" s="3"/>
-    </row>
-    <row r="63" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q62" s="3">
+        <v>0</v>
+      </c>
+      <c r="R62" s="3"/>
+    </row>
+    <row r="63" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2971,9 +3119,12 @@
       <c r="P63" s="3">
         <v>0</v>
       </c>
-      <c r="Q63" s="3"/>
-    </row>
-    <row r="64" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q63" s="3">
+        <v>0</v>
+      </c>
+      <c r="R63" s="3"/>
+    </row>
+    <row r="64" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3016,9 +3167,12 @@
       <c r="P64" s="3">
         <v>0</v>
       </c>
-      <c r="Q64" s="3"/>
-    </row>
-    <row r="65" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q64" s="3">
+        <v>0</v>
+      </c>
+      <c r="R64" s="3"/>
+    </row>
+    <row r="65" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3061,54 +3215,60 @@
       <c r="P65" s="3">
         <v>0</v>
       </c>
-      <c r="Q65" s="3"/>
-    </row>
-    <row r="66" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q65" s="3">
+        <v>0</v>
+      </c>
+      <c r="R65" s="3"/>
+    </row>
+    <row r="66" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>179078000</v>
+      </c>
+      <c r="E66" s="3">
         <v>181307000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>175412000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>137203800</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>126413800</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>104156100</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>104637200</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>102342700</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>106963000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>106615000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>84349600</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>73856900</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>72806200</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>68653100</v>
       </c>
-      <c r="Q66" s="3"/>
-    </row>
-    <row r="67" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R66" s="3"/>
+    </row>
+    <row r="67" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3126,8 +3286,9 @@
       <c r="O67" s="3"/>
       <c r="P67" s="3"/>
       <c r="Q67" s="3"/>
-    </row>
-    <row r="68" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R67" s="3"/>
+    </row>
+    <row r="68" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3170,9 +3331,12 @@
       <c r="P68" s="3">
         <v>0</v>
       </c>
-      <c r="Q68" s="3"/>
-    </row>
-    <row r="69" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q68" s="3">
+        <v>0</v>
+      </c>
+      <c r="R68" s="3"/>
+    </row>
+    <row r="69" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3215,29 +3379,32 @@
       <c r="P69" s="3">
         <v>0</v>
       </c>
-      <c r="Q69" s="3"/>
-    </row>
-    <row r="70" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q69" s="3">
+        <v>0</v>
+      </c>
+      <c r="R69" s="3"/>
+    </row>
+    <row r="70" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
       <c r="D70" s="3">
-        <v>2011000</v>
+        <v>2394000</v>
       </c>
       <c r="E70" s="3">
         <v>2011000</v>
       </c>
       <c r="F70" s="3">
+        <v>2011000</v>
+      </c>
+      <c r="G70" s="3">
         <v>1750000</v>
-      </c>
-      <c r="G70" s="3">
-        <v>1250000</v>
       </c>
       <c r="H70" s="3">
         <v>1250000</v>
       </c>
       <c r="I70" s="3">
-        <v>1231500</v>
+        <v>1250000</v>
       </c>
       <c r="J70" s="3">
         <v>1231500</v>
@@ -3252,17 +3419,20 @@
         <v>1231500</v>
       </c>
       <c r="N70" s="3">
+        <v>1231500</v>
+      </c>
+      <c r="O70" s="3">
         <v>881500</v>
       </c>
-      <c r="O70" s="3">
+      <c r="P70" s="3">
         <v>872500</v>
       </c>
-      <c r="P70" s="3">
+      <c r="Q70" s="3">
         <v>864600</v>
       </c>
-      <c r="Q70" s="3"/>
-    </row>
-    <row r="71" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R70" s="3"/>
+    </row>
+    <row r="71" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3305,54 +3475,60 @@
       <c r="P71" s="3">
         <v>0</v>
       </c>
-      <c r="Q71" s="3"/>
-    </row>
-    <row r="72" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q71" s="3">
+        <v>0</v>
+      </c>
+      <c r="R71" s="3"/>
+    </row>
+    <row r="72" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>19079000</v>
+      </c>
+      <c r="E72" s="3">
         <v>17524000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>15754000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>14646400</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>13444400</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>12820900</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>11516700</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>10164800</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>9222500</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>8430500</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>7807100</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>7188000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>6477300</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>5867200</v>
       </c>
-      <c r="Q72" s="3"/>
-    </row>
-    <row r="73" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R72" s="3"/>
+    </row>
+    <row r="73" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3395,9 +3571,12 @@
       <c r="P73" s="3">
         <v>0</v>
       </c>
-      <c r="Q73" s="3"/>
-    </row>
-    <row r="74" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q73" s="3">
+        <v>0</v>
+      </c>
+      <c r="R73" s="3"/>
+    </row>
+    <row r="74" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3440,9 +3619,12 @@
       <c r="P74" s="3">
         <v>0</v>
       </c>
-      <c r="Q74" s="3"/>
-    </row>
-    <row r="75" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q74" s="3">
+        <v>0</v>
+      </c>
+      <c r="R74" s="3"/>
+    </row>
+    <row r="75" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3485,54 +3667,60 @@
       <c r="P75" s="3">
         <v>0</v>
       </c>
-      <c r="Q75" s="3"/>
-    </row>
-    <row r="76" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q75" s="3">
+        <v>0</v>
+      </c>
+      <c r="R75" s="3"/>
+    </row>
+    <row r="76" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>26633000</v>
+      </c>
+      <c r="E76" s="3">
         <v>24946000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>23307000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>16153400</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>14937300</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>14466600</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>14228700</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>15019300</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>15255100</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>14941800</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>11104400</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>10424000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>9330100</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>8406600</v>
       </c>
-      <c r="Q76" s="3"/>
-    </row>
-    <row r="77" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R76" s="3"/>
+    </row>
+    <row r="77" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3575,104 +3763,113 @@
       <c r="P77" s="3">
         <v>0</v>
       </c>
-      <c r="Q77" s="3"/>
-    </row>
-    <row r="79" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q77" s="3">
+        <v>0</v>
+      </c>
+      <c r="R77" s="3"/>
+    </row>
+    <row r="79" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E80" s="2">
         <v>45291</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>44926</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44561</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44196</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>43830</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>43465</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>43100</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>42735</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>42369</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>42004</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>41639</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>41274</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>40908</v>
       </c>
-      <c r="Q80" s="2"/>
-    </row>
-    <row r="81" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R80" s="2"/>
+    </row>
+    <row r="81" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>2588000</v>
+      </c>
+      <c r="E81" s="3">
         <v>2741000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>1992000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>1859000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>1353200</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>1929100</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>1918100</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>1408300</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>1223500</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>987700</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>978500</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>1062400</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>953400</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>781700</v>
       </c>
-      <c r="Q81" s="3"/>
-    </row>
-    <row r="82" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R81" s="3"/>
+    </row>
+    <row r="82" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3690,53 +3887,57 @@
       <c r="O82" s="3"/>
       <c r="P82" s="3"/>
       <c r="Q82" s="3"/>
-    </row>
-    <row r="83" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R82" s="3"/>
+    </row>
+    <row r="83" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>316000</v>
+      </c>
+      <c r="E83" s="3">
         <v>304000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>282000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>224000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>220600</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>209900</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>104900</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>109600</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>149600</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>125400</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>130300</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>138400</v>
       </c>
-      <c r="O83" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P83" s="3">
+      <c r="P83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q83" s="3">
         <v>141900</v>
       </c>
-      <c r="Q83" s="3"/>
-    </row>
-    <row r="84" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R83" s="3"/>
+    </row>
+    <row r="84" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3779,9 +3980,12 @@
       <c r="P84" s="3">
         <v>0</v>
       </c>
-      <c r="Q84" s="3"/>
-    </row>
-    <row r="85" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q84" s="3">
+        <v>0</v>
+      </c>
+      <c r="R84" s="3"/>
+    </row>
+    <row r="85" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3824,9 +4028,12 @@
       <c r="P85" s="3">
         <v>0</v>
       </c>
-      <c r="Q85" s="3"/>
-    </row>
-    <row r="86" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q85" s="3">
+        <v>0</v>
+      </c>
+      <c r="R85" s="3"/>
+    </row>
+    <row r="86" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3869,9 +4076,12 @@
       <c r="P86" s="3">
         <v>0</v>
       </c>
-      <c r="Q86" s="3"/>
-    </row>
-    <row r="87" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q86" s="3">
+        <v>0</v>
+      </c>
+      <c r="R86" s="3"/>
+    </row>
+    <row r="87" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3914,9 +4124,12 @@
       <c r="P87" s="3">
         <v>0</v>
       </c>
-      <c r="Q87" s="3"/>
-    </row>
-    <row r="88" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q87" s="3">
+        <v>0</v>
+      </c>
+      <c r="R87" s="3"/>
+    </row>
+    <row r="88" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3959,54 +4172,60 @@
       <c r="P88" s="3">
         <v>0</v>
       </c>
-      <c r="Q88" s="3"/>
-    </row>
-    <row r="89" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q88" s="3">
+        <v>0</v>
+      </c>
+      <c r="R88" s="3"/>
+    </row>
+    <row r="89" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>3610000</v>
+      </c>
+      <c r="E89" s="3">
         <v>3905000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>4574000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>2715000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>789200</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>2357600</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>2089900</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>2781900</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>1183400</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>1742400</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>1099000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>932300</v>
-      </c>
-      <c r="O89" s="3">
-        <v>1772200</v>
       </c>
       <c r="P89" s="3">
         <v>1772200</v>
       </c>
-      <c r="Q89" s="3"/>
-    </row>
-    <row r="90" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q89" s="3">
+        <v>1772200</v>
+      </c>
+      <c r="R89" s="3"/>
+    </row>
+    <row r="90" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4024,53 +4243,57 @@
       <c r="O90" s="3"/>
       <c r="P90" s="3"/>
       <c r="Q90" s="3"/>
-    </row>
-    <row r="91" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R90" s="3"/>
+    </row>
+    <row r="91" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-216000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-256000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-214000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-149000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-172300</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-178000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-97700</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-79000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-107700</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-81900</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-73200</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-129600</v>
-      </c>
-      <c r="O91" s="3">
-        <v>-70000</v>
       </c>
       <c r="P91" s="3">
         <v>-70000</v>
       </c>
-      <c r="Q91" s="3"/>
-    </row>
-    <row r="92" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q91" s="3">
+        <v>-70000</v>
+      </c>
+      <c r="R91" s="3"/>
+    </row>
+    <row r="92" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4113,9 +4336,12 @@
       <c r="P92" s="3">
         <v>0</v>
       </c>
-      <c r="Q92" s="3"/>
-    </row>
-    <row r="93" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q92" s="3">
+        <v>0</v>
+      </c>
+      <c r="R92" s="3"/>
+    </row>
+    <row r="93" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4158,54 +4384,60 @@
       <c r="P93" s="3">
         <v>0</v>
       </c>
-      <c r="Q93" s="3"/>
-    </row>
-    <row r="94" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q93" s="3">
+        <v>0</v>
+      </c>
+      <c r="R93" s="3"/>
+    </row>
+    <row r="94" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-550000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-7874000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>16592000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-13631000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-22020500</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>727000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-1410100</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>3394900</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-720800</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>7714300</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-11710400</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-2203600</v>
       </c>
-      <c r="O94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P94" s="3">
+      <c r="P94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q94" s="3">
         <v>368900</v>
       </c>
-      <c r="Q94" s="3"/>
-    </row>
-    <row r="95" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R94" s="3"/>
+    </row>
+    <row r="95" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4223,53 +4455,57 @@
       <c r="O95" s="3"/>
       <c r="P95" s="3"/>
       <c r="Q95" s="3"/>
-    </row>
-    <row r="96" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R95" s="3"/>
+    </row>
+    <row r="96" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>895000</v>
+      </c>
+      <c r="E96" s="3">
         <v>868000</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>784000</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>580000</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>568100</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>552100</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>510400</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>457400</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>-523200</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>-456300</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>-441400</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>-418800</v>
-      </c>
-      <c r="O96" s="3">
-        <v>-398300</v>
       </c>
       <c r="P96" s="3">
         <v>-398300</v>
       </c>
-      <c r="Q96" s="3"/>
-    </row>
-    <row r="97" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q96" s="3">
+        <v>-398300</v>
+      </c>
+      <c r="R96" s="3"/>
+    </row>
+    <row r="97" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4312,9 +4548,12 @@
       <c r="P97" s="3">
         <v>0</v>
       </c>
-      <c r="Q97" s="3"/>
-    </row>
-    <row r="98" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q97" s="3">
+        <v>0</v>
+      </c>
+      <c r="R97" s="3"/>
+    </row>
+    <row r="98" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4357,9 +4596,12 @@
       <c r="P98" s="3">
         <v>0</v>
       </c>
-      <c r="Q98" s="3"/>
-    </row>
-    <row r="99" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q98" s="3">
+        <v>0</v>
+      </c>
+      <c r="R98" s="3"/>
+    </row>
+    <row r="99" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4402,54 +4644,60 @@
       <c r="P99" s="3">
         <v>0</v>
       </c>
-      <c r="Q99" s="3"/>
-    </row>
-    <row r="100" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q99" s="3">
+        <v>0</v>
+      </c>
+      <c r="R99" s="3"/>
+    </row>
+    <row r="100" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-2882000</v>
+      </c>
+      <c r="E100" s="3">
         <v>4180000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-20984000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>10701000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>21347700</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-3253700</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-495300</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-6076500</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-510100</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-9462000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>10311800</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>957600</v>
       </c>
-      <c r="O100" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P100" s="3">
+      <c r="P100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q100" s="3">
         <v>-1622500</v>
       </c>
-      <c r="Q100" s="3"/>
-    </row>
-    <row r="101" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R100" s="3"/>
+    </row>
+    <row r="101" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -4474,8 +4722,8 @@
       <c r="J101" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K101" s="3">
-        <v>0</v>
+      <c r="K101" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="L101" s="3">
         <v>0</v>
@@ -4486,58 +4734,64 @@
       <c r="N101" s="3">
         <v>0</v>
       </c>
-      <c r="O101" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P101" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q101" s="3"/>
-    </row>
-    <row r="102" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="O101" s="3">
+        <v>0</v>
+      </c>
+      <c r="P101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q101" s="3">
+        <v>0</v>
+      </c>
+      <c r="R101" s="3"/>
+    </row>
+    <row r="102" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>178000</v>
+      </c>
+      <c r="E102" s="3">
         <v>211000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>182000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-215000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>116400</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-169100</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>184600</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>100300</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-47500</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-5300</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-299600</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-313700</v>
-      </c>
-      <c r="O102" s="3">
-        <v>518600</v>
       </c>
       <c r="P102" s="3">
         <v>518600</v>
       </c>
-      <c r="Q102" s="3"/>
+      <c r="Q102" s="3">
+        <v>518600</v>
+      </c>
+      <c r="R102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/AAII_Financials/Yearly/MTB_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/MTB_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="172" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="179" uniqueCount="92">
   <si>
     <t>MTB</t>
   </si>
@@ -656,125 +656,131 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:R102"/>
+  <dimension ref="A5:S102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="13" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="14" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:19" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E7" s="2">
         <v>45657</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45291</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44926</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44561</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44196</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>43830</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>43465</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>43100</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>42735</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>42369</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>42004</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>41639</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>41274</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>40908</v>
       </c>
-      <c r="R7" s="2"/>
-    </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S7" s="2"/>
+    </row>
+    <row r="8" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>9185000</v>
+      </c>
+      <c r="E8" s="3">
         <v>8669000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>8998000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>7662000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>6067000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>5154800</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>5967900</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>5796300</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>5464200</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>3895900</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>3170800</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>2956900</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>2957300</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>2941700</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>2792100</v>
       </c>
-      <c r="R8" s="3"/>
-    </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S8" s="3"/>
+    </row>
+    <row r="9" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
@@ -820,39 +826,42 @@
       <c r="Q9" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="R9" s="3"/>
-    </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="R9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S9" s="3"/>
+    </row>
+    <row r="10" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>9185000</v>
+      </c>
+      <c r="E10" s="3">
         <v>8669000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>8998000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>7662000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>6067000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>5154800</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>5967900</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>5796300</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>5464200</v>
       </c>
-      <c r="L10" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="M10" s="3" t="s">
         <v>5</v>
       </c>
@@ -868,9 +877,12 @@
       <c r="Q10" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="R10" s="3"/>
-    </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="R10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S10" s="3"/>
+    </row>
+    <row r="11" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -889,8 +901,9 @@
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
       <c r="R11" s="3"/>
-    </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S11" s="3"/>
+    </row>
+    <row r="12" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -936,9 +949,12 @@
       <c r="Q12" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="R12" s="3"/>
-    </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="R12" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S12" s="3"/>
+    </row>
+    <row r="13" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -984,38 +1000,41 @@
       <c r="Q13" s="3">
         <v>0</v>
       </c>
-      <c r="R13" s="3"/>
-    </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="R13" s="3">
+        <v>0</v>
+      </c>
+      <c r="S13" s="3"/>
+    </row>
+    <row r="14" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3">
-        <v>27000</v>
+      <c r="D14" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="E14" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="F14" s="3">
+      <c r="F14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G14" s="3">
         <v>338000</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>44000</v>
       </c>
-      <c r="H14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I14" s="3">
+      <c r="I14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J14" s="3">
         <v>50000</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>135000</v>
       </c>
-      <c r="K14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="L14" s="3">
-        <v>0</v>
+      <c r="L14" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="M14" s="3">
         <v>0</v>
@@ -1032,57 +1051,63 @@
       <c r="Q14" s="3">
         <v>0</v>
       </c>
-      <c r="R14" s="3"/>
-    </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="R14" s="3">
+        <v>0</v>
+      </c>
+      <c r="S14" s="3"/>
+    </row>
+    <row r="15" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>498000</v>
+      </c>
+      <c r="E15" s="3">
         <v>508000</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>497000</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>435000</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>324000</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>320300</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>301300</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>179000</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>197100</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>-42600</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>-26400</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>-33800</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>-46900</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>-60600</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>-61600</v>
       </c>
-      <c r="R15" s="3"/>
-    </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S15" s="3"/>
+    </row>
+    <row r="16" spans="1:19" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1098,104 +1123,111 @@
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
       <c r="R16" s="3"/>
-    </row>
-    <row r="17" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S16" s="3"/>
+    </row>
+    <row r="17" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>5133000</v>
+        <v>5401000</v>
       </c>
       <c r="E17" s="3">
+        <v>5160000</v>
+      </c>
+      <c r="F17" s="3">
         <v>5002000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>4566000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>3488000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>3316600</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>3309700</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>3060000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>3007100</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>616000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>498300</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>404400</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>469100</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>547200</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>672300</v>
       </c>
-      <c r="R17" s="3"/>
-    </row>
-    <row r="18" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S17" s="3"/>
+    </row>
+    <row r="18" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>3536000</v>
+        <v>3784000</v>
       </c>
       <c r="E18" s="3">
+        <v>3509000</v>
+      </c>
+      <c r="F18" s="3">
         <v>3996000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>3096000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>2579000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>1838200</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>2658300</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>2736300</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>2457100</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>3279900</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>2672600</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>2552400</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>2488200</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>2394500</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>2119800</v>
       </c>
-      <c r="R18" s="3"/>
-    </row>
-    <row r="19" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S18" s="3"/>
+    </row>
+    <row r="19" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1214,104 +1246,111 @@
       <c r="P19" s="3"/>
       <c r="Q19" s="3"/>
       <c r="R19" s="3"/>
-    </row>
-    <row r="20" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S19" s="3"/>
+    </row>
+    <row r="20" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>92000</v>
+      </c>
+      <c r="E20" s="3">
         <v>199000</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>377000</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>146000</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>80000</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>68700</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>61000</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>93000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>133200</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-1221500</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-997900</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-910200</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-770700</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-842000</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-895200</v>
       </c>
-      <c r="R20" s="3"/>
-    </row>
-    <row r="21" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S20" s="3"/>
+    </row>
+    <row r="21" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>3845000</v>
+        <v>4190000</v>
       </c>
       <c r="E21" s="3">
+        <v>3818000</v>
+      </c>
+      <c r="F21" s="3">
         <v>4116000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>3385000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>2823000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>2089800</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>2898600</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>2822200</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>2521000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>2208000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>1800100</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>1772600</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>1855900</v>
       </c>
-      <c r="P21" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q21" s="3">
+      <c r="Q21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R21" s="3">
         <v>1366500</v>
       </c>
-      <c r="R21" s="3"/>
-    </row>
-    <row r="22" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S21" s="3"/>
+    </row>
+    <row r="22" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1339,8 +1378,8 @@
       <c r="K22" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="L22" s="3">
-        <v>0</v>
+      <c r="L22" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="M22" s="3">
         <v>0</v>
@@ -1357,105 +1396,114 @@
       <c r="Q22" s="3">
         <v>0</v>
       </c>
-      <c r="R22" s="3"/>
-    </row>
-    <row r="23" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R22" s="3">
+        <v>0</v>
+      </c>
+      <c r="S22" s="3"/>
+    </row>
+    <row r="23" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>3692000</v>
+      </c>
+      <c r="E23" s="3">
         <v>3310000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>3619000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>2612000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>2455000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>1769500</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>2547300</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>2508200</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>2323900</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>2058400</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>1674700</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>1642200</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>1717500</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>1552500</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>1224600</v>
       </c>
-      <c r="R23" s="3"/>
-    </row>
-    <row r="24" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S23" s="3"/>
+    </row>
+    <row r="24" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>841000</v>
+      </c>
+      <c r="E24" s="3">
         <v>722000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>878000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>620000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>596000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>416400</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>618100</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>590200</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>915600</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>743300</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>595000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>576000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>579100</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>523000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>365100</v>
       </c>
-      <c r="R24" s="3"/>
-    </row>
-    <row r="25" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S24" s="3"/>
+    </row>
+    <row r="25" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1501,105 +1549,114 @@
       <c r="Q25" s="3">
         <v>0</v>
       </c>
-      <c r="R25" s="3"/>
-    </row>
-    <row r="26" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R25" s="3">
+        <v>0</v>
+      </c>
+      <c r="S25" s="3"/>
+    </row>
+    <row r="26" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>2851000</v>
+      </c>
+      <c r="E26" s="3">
         <v>2588000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>2741000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>1992000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>1859000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>1353200</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>1929100</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>1918100</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>1408300</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>1315100</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>1079700</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>1066200</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>1138500</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>1029500</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>859500</v>
       </c>
-      <c r="R26" s="3"/>
-    </row>
-    <row r="27" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S26" s="3"/>
+    </row>
+    <row r="27" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>2699000</v>
+      </c>
+      <c r="E27" s="3">
         <v>2449000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>2636000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>1891000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>1777000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>1279100</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>1849500</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>1836000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>1327500</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>1223500</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>987700</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>978500</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>1062400</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>953400</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>781700</v>
       </c>
-      <c r="R27" s="3"/>
-    </row>
-    <row r="28" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S27" s="3"/>
+    </row>
+    <row r="28" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1645,9 +1702,12 @@
       <c r="Q28" s="3">
         <v>0</v>
       </c>
-      <c r="R28" s="3"/>
-    </row>
-    <row r="29" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R28" s="3">
+        <v>0</v>
+      </c>
+      <c r="S28" s="3"/>
+    </row>
+    <row r="29" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1675,8 +1735,8 @@
       <c r="K29" s="3">
         <v>0</v>
       </c>
-      <c r="L29" s="3" t="s">
-        <v>5</v>
+      <c r="L29" s="3">
+        <v>0</v>
       </c>
       <c r="M29" s="3" t="s">
         <v>5</v>
@@ -1693,9 +1753,12 @@
       <c r="Q29" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="R29" s="3"/>
-    </row>
-    <row r="30" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S29" s="3"/>
+    </row>
+    <row r="30" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1741,9 +1804,12 @@
       <c r="Q30" s="3">
         <v>0</v>
       </c>
-      <c r="R30" s="3"/>
-    </row>
-    <row r="31" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R30" s="3">
+        <v>0</v>
+      </c>
+      <c r="S30" s="3"/>
+    </row>
+    <row r="31" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1789,105 +1855,114 @@
       <c r="Q31" s="3">
         <v>0</v>
       </c>
-      <c r="R31" s="3"/>
-    </row>
-    <row r="32" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R31" s="3">
+        <v>0</v>
+      </c>
+      <c r="S31" s="3"/>
+    </row>
+    <row r="32" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-92000</v>
+      </c>
+      <c r="E32" s="3">
         <v>-199000</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-377000</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-146000</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-80000</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-68700</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-61000</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-93000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-133200</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>1221500</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>997900</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>910200</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>770700</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>842000</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>895200</v>
       </c>
-      <c r="R32" s="3"/>
-    </row>
-    <row r="33" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S32" s="3"/>
+    </row>
+    <row r="33" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>2851000</v>
+      </c>
+      <c r="E33" s="3">
         <v>2588000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>2741000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>1992000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>1859000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>1353200</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>1929100</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>1918100</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>1408300</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>1223500</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>987700</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>978500</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>1062400</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>953400</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>781700</v>
       </c>
-      <c r="R33" s="3"/>
-    </row>
-    <row r="34" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S33" s="3"/>
+    </row>
+    <row r="34" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1933,110 +2008,119 @@
       <c r="Q34" s="3">
         <v>0</v>
       </c>
-      <c r="R34" s="3"/>
-    </row>
-    <row r="35" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R34" s="3">
+        <v>0</v>
+      </c>
+      <c r="S34" s="3"/>
+    </row>
+    <row r="35" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>2851000</v>
+      </c>
+      <c r="E35" s="3">
         <v>2588000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>2741000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>1992000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>1859000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>1353200</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>1929100</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>1918100</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>1408300</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>1223500</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>987700</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>978500</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>1062400</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>953400</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>781700</v>
       </c>
-      <c r="R35" s="3"/>
-    </row>
-    <row r="37" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S35" s="3"/>
+    </row>
+    <row r="37" spans="2:19" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E38" s="2">
         <v>45657</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45291</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44926</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44561</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44196</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>43830</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>43465</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>43100</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>42735</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>42369</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>42004</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>41639</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>41274</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>40908</v>
       </c>
-      <c r="R38" s="2"/>
-    </row>
-    <row r="39" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S38" s="2"/>
+    </row>
+    <row r="39" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2055,8 +2139,9 @@
       <c r="P39" s="3"/>
       <c r="Q39" s="3"/>
       <c r="R39" s="3"/>
-    </row>
-    <row r="40" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S39" s="3"/>
+    </row>
+    <row r="40" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2075,133 +2160,140 @@
       <c r="P40" s="3"/>
       <c r="Q40" s="3"/>
       <c r="R40" s="3"/>
-    </row>
-    <row r="41" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S40" s="3"/>
+    </row>
+    <row r="41" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>1909000</v>
+        <v>18769000</v>
       </c>
       <c r="E41" s="3">
+        <v>20782000</v>
+      </c>
+      <c r="F41" s="3">
         <v>1731000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>1520000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>1337600</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>1552700</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>770300</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>921400</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>741500</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>1320500</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>1368000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>1290000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>1573400</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>1983600</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>1449500</v>
       </c>
-      <c r="R41" s="3"/>
-    </row>
-    <row r="42" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S41" s="3"/>
+    </row>
+    <row r="42" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>19207000</v>
+        <v>342000</v>
       </c>
       <c r="E42" s="3">
+        <v>356000</v>
+      </c>
+      <c r="F42" s="3">
         <v>28477000</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>25489000</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>42343500</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>24760900</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>7655700</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>8289400</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>5201500</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>6064700</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>8672000</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>7481500</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>2816200</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>924600</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>1086500</v>
       </c>
-      <c r="R42" s="3"/>
-    </row>
-    <row r="43" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S42" s="3"/>
+    </row>
+    <row r="43" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>75000</v>
+      </c>
+      <c r="E43" s="3">
         <v>72000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>68000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>74000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>68000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>67000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>62000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>56000</v>
       </c>
-      <c r="K43" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="L43" s="3">
-        <v>0</v>
+      <c r="L43" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="M43" s="3">
         <v>0</v>
@@ -2218,9 +2310,12 @@
       <c r="Q43" s="3">
         <v>0</v>
       </c>
-      <c r="R43" s="3"/>
-    </row>
-    <row r="44" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R43" s="3">
+        <v>0</v>
+      </c>
+      <c r="S43" s="3"/>
+    </row>
+    <row r="44" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2228,29 +2323,29 @@
         <v>35000</v>
       </c>
       <c r="E44" s="3">
+        <v>35000</v>
+      </c>
+      <c r="F44" s="3">
         <v>39000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>41000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>23900</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>34700</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>85600</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>78400</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>111900</v>
       </c>
-      <c r="L44" s="3">
-        <v>0</v>
-      </c>
       <c r="M44" s="3">
         <v>0</v>
       </c>
@@ -2266,39 +2361,42 @@
       <c r="Q44" s="3">
         <v>0</v>
       </c>
-      <c r="R44" s="3"/>
-    </row>
-    <row r="45" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R44" s="3">
+        <v>0</v>
+      </c>
+      <c r="S44" s="3"/>
+    </row>
+    <row r="45" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>6773000</v>
+        <v>8310000</v>
       </c>
       <c r="E45" s="3">
-        <v>6629000</v>
+        <v>6877000</v>
       </c>
       <c r="F45" s="3">
+        <v>6500000</v>
+      </c>
+      <c r="G45" s="3">
         <v>669000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>356200</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>440900</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>354100</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>375000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>350200</v>
       </c>
-      <c r="L45" s="3">
-        <v>0</v>
-      </c>
       <c r="M45" s="3">
         <v>0</v>
       </c>
@@ -2314,39 +2412,42 @@
       <c r="Q45" s="3">
         <v>0</v>
       </c>
-      <c r="R45" s="3"/>
-    </row>
-    <row r="46" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R45" s="3">
+        <v>0</v>
+      </c>
+      <c r="S45" s="3"/>
+    </row>
+    <row r="46" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>27996000</v>
+        <v>28456000</v>
       </c>
       <c r="E46" s="3">
-        <v>36944000</v>
+        <v>28643000</v>
       </c>
       <c r="F46" s="3">
+        <v>36815000</v>
+      </c>
+      <c r="G46" s="3">
         <v>27956000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>45028100</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>27911200</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>10035800</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>10956200</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>7462500</v>
       </c>
-      <c r="L46" s="3">
-        <v>0</v>
-      </c>
       <c r="M46" s="3">
         <v>0</v>
       </c>
@@ -2362,39 +2463,42 @@
       <c r="Q46" s="3">
         <v>0</v>
       </c>
-      <c r="R46" s="3"/>
-    </row>
-    <row r="47" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R46" s="3">
+        <v>0</v>
+      </c>
+      <c r="S46" s="3"/>
+    </row>
+    <row r="47" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>38616000</v>
+      </c>
+      <c r="E47" s="3">
         <v>35607000</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>28358000</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>25211000</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>7155900</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>7045700</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>9497300</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>12692800</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>14664500</v>
       </c>
-      <c r="L47" s="3">
-        <v>0</v>
-      </c>
       <c r="M47" s="3">
         <v>0</v>
       </c>
@@ -2410,105 +2514,114 @@
       <c r="Q47" s="3">
         <v>0</v>
       </c>
-      <c r="R47" s="3"/>
-    </row>
-    <row r="48" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R47" s="3">
+        <v>0</v>
+      </c>
+      <c r="S47" s="3"/>
+    </row>
+    <row r="48" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>1705000</v>
+        <v>1813000</v>
       </c>
       <c r="E48" s="3">
-        <v>1739000</v>
+        <v>1909000</v>
       </c>
       <c r="F48" s="3">
+        <v>1939000</v>
+      </c>
+      <c r="G48" s="3">
         <v>1654000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>1144800</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>1161600</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>1140900</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>647400</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>646500</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>675300</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>666700</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>613000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>633500</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>594700</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>581400</v>
       </c>
-      <c r="R48" s="3"/>
-    </row>
-    <row r="49" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S48" s="3"/>
+    </row>
+    <row r="49" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>9383000</v>
+        <v>8948000</v>
       </c>
       <c r="E49" s="3">
-        <v>9262000</v>
+        <v>9053000</v>
       </c>
       <c r="F49" s="3">
+        <v>9191000</v>
+      </c>
+      <c r="G49" s="3">
         <v>8948000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>4946800</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>4941900</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>4990200</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>4875400</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>4893800</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>4690800</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>4733400</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>3559700</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>3593500</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>3640400</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>3701000</v>
       </c>
-      <c r="R49" s="3"/>
-    </row>
-    <row r="50" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S49" s="3"/>
+    </row>
+    <row r="50" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2554,9 +2667,12 @@
       <c r="Q50" s="3">
         <v>0</v>
       </c>
-      <c r="R50" s="3"/>
-    </row>
-    <row r="51" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R50" s="3">
+        <v>0</v>
+      </c>
+      <c r="S50" s="3"/>
+    </row>
+    <row r="51" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2602,39 +2718,42 @@
       <c r="Q51" s="3">
         <v>0</v>
       </c>
-      <c r="R51" s="3"/>
-    </row>
-    <row r="52" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R51" s="3">
+        <v>0</v>
+      </c>
+      <c r="S51" s="3"/>
+    </row>
+    <row r="52" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>16000</v>
+      </c>
+      <c r="E52" s="3">
         <v>17000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>22000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>7485000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>6287400</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>5796300</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>4778700</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>4030600</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>4332500</v>
       </c>
-      <c r="L52" s="3">
-        <v>0</v>
-      </c>
       <c r="M52" s="3">
         <v>0</v>
       </c>
@@ -2650,9 +2769,12 @@
       <c r="Q52" s="3">
         <v>0</v>
       </c>
-      <c r="R52" s="3"/>
-    </row>
-    <row r="53" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R52" s="3">
+        <v>0</v>
+      </c>
+      <c r="S52" s="3"/>
+    </row>
+    <row r="53" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2698,57 +2820,63 @@
       <c r="Q53" s="3">
         <v>0</v>
       </c>
-      <c r="R53" s="3"/>
-    </row>
-    <row r="54" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R53" s="3">
+        <v>0</v>
+      </c>
+      <c r="S53" s="3"/>
+    </row>
+    <row r="54" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>213510000</v>
+      </c>
+      <c r="E54" s="3">
         <v>208105000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>208264000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>200730000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>155107200</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>142601100</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>119872800</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>120097400</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>118593500</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>123449000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>122788000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>96685500</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>85162400</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>83008800</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>77924300</v>
       </c>
-      <c r="R54" s="3"/>
-    </row>
-    <row r="55" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S54" s="3"/>
+    </row>
+    <row r="55" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2767,8 +2895,9 @@
       <c r="P55" s="3"/>
       <c r="Q55" s="3"/>
       <c r="R55" s="3"/>
-    </row>
-    <row r="56" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S55" s="3"/>
+    </row>
+    <row r="56" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2787,86 +2916,90 @@
       <c r="P56" s="3"/>
       <c r="Q56" s="3"/>
       <c r="R56" s="3"/>
-    </row>
-    <row r="57" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S56" s="3"/>
+    </row>
+    <row r="57" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>166909000</v>
+      </c>
+      <c r="E57" s="3">
         <v>161095000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>163274000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>163515000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>131543400</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>119805700</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>94770100</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>90156600</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>92432100</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>1634600</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>1708100</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>1355900</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>1114700</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>1512700</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>1790100</v>
       </c>
-      <c r="R57" s="3"/>
-    </row>
-    <row r="58" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S57" s="3"/>
+    </row>
+    <row r="58" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>2042000</v>
+        <v>2756000</v>
       </c>
       <c r="E58" s="3">
+        <v>1882000</v>
+      </c>
+      <c r="F58" s="3">
         <v>6259000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>5654000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>1044800</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>1050000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>2057900</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>5234900</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>1014200</v>
       </c>
-      <c r="L58" s="3">
-        <v>0</v>
-      </c>
       <c r="M58" s="3">
         <v>0</v>
       </c>
@@ -2882,9 +3015,12 @@
       <c r="Q58" s="3">
         <v>0</v>
       </c>
-      <c r="R58" s="3"/>
-    </row>
-    <row r="59" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R58" s="3">
+        <v>0</v>
+      </c>
+      <c r="S58" s="3"/>
+    </row>
+    <row r="59" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
@@ -2924,45 +3060,48 @@
       <c r="O59" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="P59" s="3">
-        <v>0</v>
+      <c r="P59" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="Q59" s="3">
         <v>0</v>
       </c>
-      <c r="R59" s="3"/>
-    </row>
-    <row r="60" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R59" s="3">
+        <v>0</v>
+      </c>
+      <c r="S59" s="3"/>
+    </row>
+    <row r="60" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>165229000</v>
+        <v>171812000</v>
       </c>
       <c r="E60" s="3">
+        <v>165009000</v>
+      </c>
+      <c r="F60" s="3">
         <v>171697000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>169250000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>132629000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>120915600</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>96933400</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>95486700</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>93522000</v>
       </c>
-      <c r="L60" s="3">
-        <v>0</v>
-      </c>
       <c r="M60" s="3">
         <v>0</v>
       </c>
@@ -2978,87 +3117,93 @@
       <c r="Q60" s="3">
         <v>0</v>
       </c>
-      <c r="R60" s="3"/>
-    </row>
-    <row r="61" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R60" s="3">
+        <v>0</v>
+      </c>
+      <c r="S60" s="3"/>
+    </row>
+    <row r="61" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>13122000</v>
+        <v>11410000</v>
       </c>
       <c r="E61" s="3">
+        <v>13282000</v>
+      </c>
+      <c r="F61" s="3">
         <v>8918000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>3930000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>3012500</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>3999200</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>5565700</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>7799100</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>7441500</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>9493800</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>10653900</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>9007000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>5108900</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>3177700</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>3887800</v>
       </c>
-      <c r="R61" s="3"/>
-    </row>
-    <row r="62" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S61" s="3"/>
+    </row>
+    <row r="62" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>670000</v>
+        <v>1057000</v>
       </c>
       <c r="E62" s="3">
+        <v>730000</v>
+      </c>
+      <c r="F62" s="3">
         <v>638000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>2184000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>1517200</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>1457000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>1614000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>1308400</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>1379200</v>
       </c>
-      <c r="L62" s="3">
-        <v>0</v>
-      </c>
       <c r="M62" s="3">
         <v>0</v>
       </c>
@@ -3074,9 +3219,12 @@
       <c r="Q62" s="3">
         <v>0</v>
       </c>
-      <c r="R62" s="3"/>
-    </row>
-    <row r="63" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R62" s="3">
+        <v>0</v>
+      </c>
+      <c r="S62" s="3"/>
+    </row>
+    <row r="63" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3122,9 +3270,12 @@
       <c r="Q63" s="3">
         <v>0</v>
       </c>
-      <c r="R63" s="3"/>
-    </row>
-    <row r="64" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R63" s="3">
+        <v>0</v>
+      </c>
+      <c r="S63" s="3"/>
+    </row>
+    <row r="64" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3170,9 +3321,12 @@
       <c r="Q64" s="3">
         <v>0</v>
       </c>
-      <c r="R64" s="3"/>
-    </row>
-    <row r="65" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R64" s="3">
+        <v>0</v>
+      </c>
+      <c r="S64" s="3"/>
+    </row>
+    <row r="65" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3218,57 +3372,63 @@
       <c r="Q65" s="3">
         <v>0</v>
       </c>
-      <c r="R65" s="3"/>
-    </row>
-    <row r="66" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R65" s="3">
+        <v>0</v>
+      </c>
+      <c r="S65" s="3"/>
+    </row>
+    <row r="66" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>184333000</v>
+      </c>
+      <c r="E66" s="3">
         <v>179078000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>181307000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>175412000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>137203800</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>126413800</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>104156100</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>104637200</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>102342700</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>106963000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>106615000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>84349600</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>73856900</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>72806200</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>68653100</v>
       </c>
-      <c r="R66" s="3"/>
-    </row>
-    <row r="67" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S66" s="3"/>
+    </row>
+    <row r="67" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3287,8 +3447,9 @@
       <c r="P67" s="3"/>
       <c r="Q67" s="3"/>
       <c r="R67" s="3"/>
-    </row>
-    <row r="68" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S67" s="3"/>
+    </row>
+    <row r="68" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3334,9 +3495,12 @@
       <c r="Q68" s="3">
         <v>0</v>
       </c>
-      <c r="R68" s="3"/>
-    </row>
-    <row r="69" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R68" s="3">
+        <v>0</v>
+      </c>
+      <c r="S68" s="3"/>
+    </row>
+    <row r="69" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3382,32 +3546,35 @@
       <c r="Q69" s="3">
         <v>0</v>
       </c>
-      <c r="R69" s="3"/>
-    </row>
-    <row r="70" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R69" s="3">
+        <v>0</v>
+      </c>
+      <c r="S69" s="3"/>
+    </row>
+    <row r="70" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
       <c r="D70" s="3">
+        <v>2834000</v>
+      </c>
+      <c r="E70" s="3">
         <v>2394000</v>
-      </c>
-      <c r="E70" s="3">
-        <v>2011000</v>
       </c>
       <c r="F70" s="3">
         <v>2011000</v>
       </c>
       <c r="G70" s="3">
+        <v>2011000</v>
+      </c>
+      <c r="H70" s="3">
         <v>1750000</v>
-      </c>
-      <c r="H70" s="3">
-        <v>1250000</v>
       </c>
       <c r="I70" s="3">
         <v>1250000</v>
       </c>
       <c r="J70" s="3">
-        <v>1231500</v>
+        <v>1250000</v>
       </c>
       <c r="K70" s="3">
         <v>1231500</v>
@@ -3422,17 +3589,20 @@
         <v>1231500</v>
       </c>
       <c r="O70" s="3">
+        <v>1231500</v>
+      </c>
+      <c r="P70" s="3">
         <v>881500</v>
       </c>
-      <c r="P70" s="3">
+      <c r="Q70" s="3">
         <v>872500</v>
       </c>
-      <c r="Q70" s="3">
+      <c r="R70" s="3">
         <v>864600</v>
       </c>
-      <c r="R70" s="3"/>
-    </row>
-    <row r="71" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S70" s="3"/>
+    </row>
+    <row r="71" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3478,57 +3648,63 @@
       <c r="Q71" s="3">
         <v>0</v>
       </c>
-      <c r="R71" s="3"/>
-    </row>
-    <row r="72" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R71" s="3">
+        <v>0</v>
+      </c>
+      <c r="S71" s="3"/>
+    </row>
+    <row r="72" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>20882000</v>
+      </c>
+      <c r="E72" s="3">
         <v>19079000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>17524000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>15754000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>14646400</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>13444400</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>12820900</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>11516700</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>10164800</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>9222500</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>8430500</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>7807100</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>7188000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>6477300</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>5867200</v>
       </c>
-      <c r="R72" s="3"/>
-    </row>
-    <row r="73" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S72" s="3"/>
+    </row>
+    <row r="73" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3574,9 +3750,12 @@
       <c r="Q73" s="3">
         <v>0</v>
       </c>
-      <c r="R73" s="3"/>
-    </row>
-    <row r="74" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R73" s="3">
+        <v>0</v>
+      </c>
+      <c r="S73" s="3"/>
+    </row>
+    <row r="74" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3622,9 +3801,12 @@
       <c r="Q74" s="3">
         <v>0</v>
       </c>
-      <c r="R74" s="3"/>
-    </row>
-    <row r="75" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R74" s="3">
+        <v>0</v>
+      </c>
+      <c r="S74" s="3"/>
+    </row>
+    <row r="75" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3670,57 +3852,63 @@
       <c r="Q75" s="3">
         <v>0</v>
       </c>
-      <c r="R75" s="3"/>
-    </row>
-    <row r="76" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R75" s="3">
+        <v>0</v>
+      </c>
+      <c r="S75" s="3"/>
+    </row>
+    <row r="76" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>26343000</v>
+      </c>
+      <c r="E76" s="3">
         <v>26633000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>24946000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>23307000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>16153400</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>14937300</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>14466600</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>14228700</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>15019300</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>15255100</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>14941800</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>11104400</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>10424000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>9330100</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>8406600</v>
       </c>
-      <c r="R76" s="3"/>
-    </row>
-    <row r="77" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S76" s="3"/>
+    </row>
+    <row r="77" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3766,110 +3954,119 @@
       <c r="Q77" s="3">
         <v>0</v>
       </c>
-      <c r="R77" s="3"/>
-    </row>
-    <row r="79" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R77" s="3">
+        <v>0</v>
+      </c>
+      <c r="S77" s="3"/>
+    </row>
+    <row r="79" spans="2:19" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E80" s="2">
         <v>45657</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45291</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44926</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44561</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44196</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>43830</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>43465</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>43100</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>42735</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>42369</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>42004</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>41639</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>41274</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>40908</v>
       </c>
-      <c r="R80" s="2"/>
-    </row>
-    <row r="81" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S80" s="2"/>
+    </row>
+    <row r="81" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>2851000</v>
+      </c>
+      <c r="E81" s="3">
         <v>2588000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>2741000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>1992000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>1859000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>1353200</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>1929100</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>1918100</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>1408300</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>1223500</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>987700</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>978500</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>1062400</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>953400</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>781700</v>
       </c>
-      <c r="R81" s="3"/>
-    </row>
-    <row r="82" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S81" s="3"/>
+    </row>
+    <row r="82" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3888,56 +4085,60 @@
       <c r="P82" s="3"/>
       <c r="Q82" s="3"/>
       <c r="R82" s="3"/>
-    </row>
-    <row r="83" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S82" s="3"/>
+    </row>
+    <row r="83" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>323000</v>
+      </c>
+      <c r="E83" s="3">
         <v>316000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>304000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>282000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>224000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>220600</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>209900</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>104900</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>109600</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>149600</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>125400</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>130300</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>138400</v>
       </c>
-      <c r="P83" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q83" s="3">
+      <c r="Q83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R83" s="3">
         <v>141900</v>
       </c>
-      <c r="R83" s="3"/>
-    </row>
-    <row r="84" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S83" s="3"/>
+    </row>
+    <row r="84" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3983,9 +4184,12 @@
       <c r="Q84" s="3">
         <v>0</v>
       </c>
-      <c r="R84" s="3"/>
-    </row>
-    <row r="85" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R84" s="3">
+        <v>0</v>
+      </c>
+      <c r="S84" s="3"/>
+    </row>
+    <row r="85" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4031,9 +4235,12 @@
       <c r="Q85" s="3">
         <v>0</v>
       </c>
-      <c r="R85" s="3"/>
-    </row>
-    <row r="86" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R85" s="3">
+        <v>0</v>
+      </c>
+      <c r="S85" s="3"/>
+    </row>
+    <row r="86" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4079,9 +4286,12 @@
       <c r="Q86" s="3">
         <v>0</v>
       </c>
-      <c r="R86" s="3"/>
-    </row>
-    <row r="87" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R86" s="3">
+        <v>0</v>
+      </c>
+      <c r="S86" s="3"/>
+    </row>
+    <row r="87" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4127,9 +4337,12 @@
       <c r="Q87" s="3">
         <v>0</v>
       </c>
-      <c r="R87" s="3"/>
-    </row>
-    <row r="88" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R87" s="3">
+        <v>0</v>
+      </c>
+      <c r="S87" s="3"/>
+    </row>
+    <row r="88" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4175,57 +4388,63 @@
       <c r="Q88" s="3">
         <v>0</v>
       </c>
-      <c r="R88" s="3"/>
-    </row>
-    <row r="89" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R88" s="3">
+        <v>0</v>
+      </c>
+      <c r="S88" s="3"/>
+    </row>
+    <row r="89" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>3003000</v>
+      </c>
+      <c r="E89" s="3">
         <v>3610000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>3905000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>4574000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>2715000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>789200</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>2357600</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>2089900</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>2781900</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>1183400</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>1742400</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>1099000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>932300</v>
-      </c>
-      <c r="P89" s="3">
-        <v>1772200</v>
       </c>
       <c r="Q89" s="3">
         <v>1772200</v>
       </c>
-      <c r="R89" s="3"/>
-    </row>
-    <row r="90" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R89" s="3">
+        <v>1772200</v>
+      </c>
+      <c r="S89" s="3"/>
+    </row>
+    <row r="90" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4244,56 +4463,60 @@
       <c r="P90" s="3"/>
       <c r="Q90" s="3"/>
       <c r="R90" s="3"/>
-    </row>
-    <row r="91" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S90" s="3"/>
+    </row>
+    <row r="91" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-143000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-216000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-256000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-214000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-149000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-172300</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-178000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-97700</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-79000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-107700</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-81900</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-73200</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-129600</v>
-      </c>
-      <c r="P91" s="3">
-        <v>-70000</v>
       </c>
       <c r="Q91" s="3">
         <v>-70000</v>
       </c>
-      <c r="R91" s="3"/>
-    </row>
-    <row r="92" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R91" s="3">
+        <v>-70000</v>
+      </c>
+      <c r="S91" s="3"/>
+    </row>
+    <row r="92" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4339,9 +4562,12 @@
       <c r="Q92" s="3">
         <v>0</v>
       </c>
-      <c r="R92" s="3"/>
-    </row>
-    <row r="93" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R92" s="3">
+        <v>0</v>
+      </c>
+      <c r="S92" s="3"/>
+    </row>
+    <row r="93" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4387,57 +4613,63 @@
       <c r="Q93" s="3">
         <v>0</v>
       </c>
-      <c r="R93" s="3"/>
-    </row>
-    <row r="94" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R93" s="3">
+        <v>0</v>
+      </c>
+      <c r="S93" s="3"/>
+    </row>
+    <row r="94" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>-550000</v>
+        <v>-6816000</v>
       </c>
       <c r="E94" s="3">
-        <v>-7874000</v>
+        <v>-9746000</v>
       </c>
       <c r="F94" s="3">
+        <v>-4764000</v>
+      </c>
+      <c r="G94" s="3">
         <v>16592000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-13631000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-22020500</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>727000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-1410100</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>3394900</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-720800</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>7714300</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-11710400</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-2203600</v>
       </c>
-      <c r="P94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q94" s="3">
+      <c r="Q94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R94" s="3">
         <v>368900</v>
       </c>
-      <c r="R94" s="3"/>
-    </row>
-    <row r="95" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S94" s="3"/>
+    </row>
+    <row r="95" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4456,56 +4688,60 @@
       <c r="P95" s="3"/>
       <c r="Q95" s="3"/>
       <c r="R95" s="3"/>
-    </row>
-    <row r="96" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S95" s="3"/>
+    </row>
+    <row r="96" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>899000</v>
+      </c>
+      <c r="E96" s="3">
         <v>895000</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>868000</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>784000</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>580000</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>568100</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>552100</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>510400</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>457400</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>-523200</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>-456300</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>-441400</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>-418800</v>
-      </c>
-      <c r="P96" s="3">
-        <v>-398300</v>
       </c>
       <c r="Q96" s="3">
         <v>-398300</v>
       </c>
-      <c r="R96" s="3"/>
-    </row>
-    <row r="97" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R96" s="3">
+        <v>-398300</v>
+      </c>
+      <c r="S96" s="3"/>
+    </row>
+    <row r="97" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4551,9 +4787,12 @@
       <c r="Q97" s="3">
         <v>0</v>
       </c>
-      <c r="R97" s="3"/>
-    </row>
-    <row r="98" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R97" s="3">
+        <v>0</v>
+      </c>
+      <c r="S97" s="3"/>
+    </row>
+    <row r="98" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4599,9 +4838,12 @@
       <c r="Q98" s="3">
         <v>0</v>
       </c>
-      <c r="R98" s="3"/>
-    </row>
-    <row r="99" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R98" s="3">
+        <v>0</v>
+      </c>
+      <c r="S98" s="3"/>
+    </row>
+    <row r="99" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4647,57 +4889,63 @@
       <c r="Q99" s="3">
         <v>0</v>
       </c>
-      <c r="R99" s="3"/>
-    </row>
-    <row r="100" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R99" s="3">
+        <v>0</v>
+      </c>
+      <c r="S99" s="3"/>
+    </row>
+    <row r="100" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>1800000</v>
+      </c>
+      <c r="E100" s="3">
         <v>-2882000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>4180000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-20984000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>10701000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>21347700</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-3253700</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-495300</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-6076500</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-510100</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-9462000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>10311800</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>957600</v>
       </c>
-      <c r="P100" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q100" s="3">
+      <c r="Q100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R100" s="3">
         <v>-1622500</v>
       </c>
-      <c r="R100" s="3"/>
-    </row>
-    <row r="101" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S100" s="3"/>
+    </row>
+    <row r="101" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -4725,8 +4973,8 @@
       <c r="K101" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="L101" s="3">
-        <v>0</v>
+      <c r="L101" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="M101" s="3">
         <v>0</v>
@@ -4737,61 +4985,67 @@
       <c r="O101" s="3">
         <v>0</v>
       </c>
-      <c r="P101" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q101" s="3">
-        <v>0</v>
-      </c>
-      <c r="R101" s="3"/>
-    </row>
-    <row r="102" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="P101" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R101" s="3">
+        <v>0</v>
+      </c>
+      <c r="S101" s="3"/>
+    </row>
+    <row r="102" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>178000</v>
+        <v>-2013000</v>
       </c>
       <c r="E102" s="3">
-        <v>211000</v>
+        <v>-9018000</v>
       </c>
       <c r="F102" s="3">
+        <v>3321000</v>
+      </c>
+      <c r="G102" s="3">
         <v>182000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-215000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>116400</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-169100</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>184600</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>100300</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-47500</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-5300</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-299600</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-313700</v>
-      </c>
-      <c r="P102" s="3">
-        <v>518600</v>
       </c>
       <c r="Q102" s="3">
         <v>518600</v>
       </c>
-      <c r="R102" s="3"/>
+      <c r="R102" s="3">
+        <v>518600</v>
+      </c>
+      <c r="S102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
